--- a/ai-results/TerraYield_Emlakci_Parsel_Eslesme_FINAL.xlsx
+++ b/ai-results/TerraYield_Emlakci_Parsel_Eslesme_FINAL.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AAYS_GITHUB_BRIDGE_CLEAN2\ai-results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{372944AE-77E9-437D-A6AB-055C800C15CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{761F14A6-6AF6-467F-BEC2-16BE77423B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2618ACBC-B2C1-4713-AB30-F85B1300649F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7AA7A21F-28D4-4842-AB3C-63544B8A9944}"/>
   </bookViews>
   <sheets>
-    <sheet name="Real100_Status" sheetId="1" r:id="rId1"/>
+    <sheet name="Final_Status" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,10 +47,10 @@
     <t>value</t>
   </si>
   <si>
-    <t>verified_candidate_rows</t>
-  </si>
-  <si>
-    <t>parcel_candidate_files</t>
+    <t>parcel_join_rows</t>
+  </si>
+  <si>
+    <t>coverage_rows</t>
   </si>
   <si>
     <t>db_write</t>
@@ -59,10 +59,10 @@
     <t>production_deploy</t>
   </si>
   <si>
-    <t>final_status</t>
-  </si>
-  <si>
-    <t>review_required_not_import_ready</t>
+    <t>real_100</t>
+  </si>
+  <si>
+    <t>false_until_approval</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D74B5F-9E5B-4B9F-89C6-CAC160A6E993}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF47F19-893E-4654-93AF-50950DC34430}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -451,7 +451,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -459,7 +459,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">

--- a/ai-results/TerraYield_Emlakci_Parsel_Eslesme_FINAL.xlsx
+++ b/ai-results/TerraYield_Emlakci_Parsel_Eslesme_FINAL.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AAYS_GITHUB_BRIDGE_CLEAN2\ai-results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AAYS_DATA\estate_agents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{761F14A6-6AF6-467F-BEC2-16BE77423B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA372AB4-281D-411D-9D84-221F65FE1B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7AA7A21F-28D4-4842-AB3C-63544B8A9944}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0BA7450C-5D03-47FF-9277-0F9FBD4489E3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Final_Status" sheetId="1" r:id="rId1"/>
+    <sheet name="geom_parse" sheetId="5" r:id="rId1"/>
+    <sheet name="parcel_join" sheetId="4" r:id="rId2"/>
+    <sheet name="coverage_groups" sheetId="3" r:id="rId3"/>
+    <sheet name="evidence_sources" sheetId="2" r:id="rId4"/>
+    <sheet name="verified_agents" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,30 +43,483 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>field</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>parcel_join_rows</t>
-  </si>
-  <si>
-    <t>coverage_rows</t>
-  </si>
-  <si>
-    <t>db_write</t>
-  </si>
-  <si>
-    <t>production_deploy</t>
-  </si>
-  <si>
-    <t>real_100</t>
-  </si>
-  <si>
-    <t>false_until_approval</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="159">
+  <si>
+    <t>agent_id</t>
+  </si>
+  <si>
+    <t>candidate_id</t>
+  </si>
+  <si>
+    <t>agent_or_branch_name</t>
+  </si>
+  <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>office_address</t>
+  </si>
+  <si>
+    <t>website_url</t>
+  </si>
+  <si>
+    <t>source_url</t>
+  </si>
+  <si>
+    <t>postcode</t>
+  </si>
+  <si>
+    <t>local_authority</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>trust_score_10</t>
+  </si>
+  <si>
+    <t>overall_data_truth_score_4</t>
+  </si>
+  <si>
+    <t>verification_status</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>source_file</t>
+  </si>
+  <si>
+    <t>EA-REVIEW-EA-CAND-000020</t>
+  </si>
+  <si>
+    <t>EA-CAND-000020</t>
+  </si>
+  <si>
+    <t>(()=&gt;{var e={603:(e,t,i)=&gt;{var r,s,n;function o(e){return"function"==typeof Symbol&amp;&amp;"symbol"==typeof Symbol.iterator?d=function(e){return typeof e}:d=function(e){return e&amp;&amp;"function"==typeof Symbol&amp;&amp;e.constructor===Symbol&amp;&amp;e!==Symbol.prototype?"symbol":typeof e},d(e)}function a(e,t,i){return"undefined"!=typeof Reflect&amp;&amp;Reflect.get?f=Reflect.get:f=function(e,t,i){var r=function(e,t){for(;!Object.prototype.hasOwnProperty.call(e,t)&amp;&amp;null!==(e=y(e)););return e}(e,t);if(r){var s=Object.getOwnPropertyDescriptor(r,t);return s.get?s.get.call(i):s.value}},f(e,t,i||e)}function l(e,t){if(!(e instanceof t))throw new TypeError("Cannot call a class as a function")}function h(e,t){for(var i=0;i&lt;t.length;i++){var r=t[i];r.enumerable=r.enumerable||!1,r.configurable=!0,"value"in r&amp;&amp;(r.writable=!0),Object.defineProperty(e,r.key,r)}}function c(e,t,i){return t&amp;&amp;h(e.prototype,t),i&amp;&amp;h(e,i),e}function u(e,t){if("function"!=typeof t&amp;&amp;null!==t)throw new TypeError("Super expression must either be null or a function");e.prototype=Object.create(t&amp;&amp;t.prototype,{constructor:{value:e,writable:!0,configurable:!0}}),t&amp;&amp;x(e,t)}function p(e){var t=v();return function(){var i,r=y(e);if(t){var s=y(this).constructor;i=Reflect.construct(r,arguments,s)}else i=r.apply(this,arguments);return function(e,t){return!t||"object"!==o(t)&amp;&amp;"function"!=typeof t?function(e){if(void 0===e)throw new ReferenceError("this hasn't been initialised - super() hasn't been called");return e}(e):t}(this,i)}}function m(e){var t="function"==typeof Map?new Map:void 0;return d=function(e){if(null===e||!function(e){return-1!==Function.toString.call(e).indexOf("[native code]")}(e))return e;if("function"!=typeof e)throw new TypeError("Super expression must either be null or a function");if(void 0!==t){if(t.has(e))return t.get(e);t.set(e,i)}function i(){return g(e,arguments,y(this).constructor)}return i.prototype=Object.create(e.prototype,{constructor:{value:i,enumerable:!1,writable:!0,configurable:!0}}),x(i,e)},d(e)}function g(e,t,i){return v()?f=Reflect.construct:f=function(e,t,i){var r=[null];r.push.apply(r,t);var s=new(Function.bind.apply(e,r));return i&amp;&amp;x(s,i.prototype),s},f.apply(null,arguments)}function v(){if("undefined"==typeof Reflect||!Reflect.construct)return!1;if(Reflect.construct.sham)return!1;if("function"==typeof Proxy)return!0;try{return Boolean.prototype.valueOf.call(Reflect.construct(Boolean,[],function(){})),!0}catch(e){return!1}}function x(e,t){return f=Object.setPrototypeOf||function(e,t){return e.__proto__=t,e},f(e,t)}function y(e){return d=Object.setPrototypeOf?Object.getPrototypeOf:function(e){return e.__proto__||Object.getPrototypeOf(e)},d(e)}!function(){if("undefined"!=typeof document){document.all&amp;&amp;!document.addEventListener||function(s,n){var o,a,l=s.document,d=(s.location,s.navigator),h=s.JQXLite,c=s.$,u=Array.prototype.push,p=Array.prototype.slice,m=Array.prototype.indexOf,f=Object.prototype.toString,g=Object.prototype.hasOwnProperty,v=String.prototype.trim,x=function(e,t){return new x.fn.init(e,t,o)},y=/[\-+]?(?:\d*\.|)\d+(?:[eE][\-+]?\d+|)/.source,w=/\S/,b=/\s+/,_=/^[\s\uFEFF\xA0]+|[\s\uFEFF\xA0]+$/g,q=/^(?:[^#&lt;]*(&lt;[\w\W]+&gt;)[^&gt;]*$|#([\w\-]*)$)/,j=/^&lt;(\w+)\s*\/?&gt;(?:&lt;\/\1&gt;|)$/,T=/^[\],:{}\s]*$/,C=/(?:^|:|,)(?:\s*\[)+/g,S=/\\(?:["\\\/bfnrt]|u[\da-fA-F]{4})/g,k=/"[^"\\\r\n]*"|true|false|null|-?(?:\d\d*\.|)\d+(?:[eE][\-+]?\d+|)/g,I=/^-ms-/,D=/-([\da-z])/gi,P=function(e,t){return(t+"").toUpperCase()},A=function(){l.addEventListener?(l.removeEventListener("DOMContentLoaded",A,!1),x.ready()):"complete"===l.readyState&amp;&amp;(l.detachEvent("onreadystatechange",A),x.ready())},M={};x.fn=x.prototype={constructor:x,init:function(e,t,i){var r,s,o;if(!e)return this;if(e.nodeType)return this.context=this[0]=e,this.length=1,this;if("string"==typeof e){if(!(r="&lt;"===e.charAt(0)&amp;&amp;"&gt;"===e.charAt(e.length-1)&amp;&amp;e.length&gt;=3?[null,e,null]:q.exec(e))||!r[1]&amp;&amp;t)return!t||t.jqx?(t||i).find(e):this.constructor(t).find(e);if(r[1])return o=(t=t instanceof x?t[0]:t)&amp;&amp;t.nodeType?t.ownerDocument||t:l,e=x.parseHTML(r[1],o,!0),j.test(r[1])&amp;&amp;x.isPlainObject(t)&amp;&amp;this.attr.call(e,t,!0),x.merge(this,e);if((s=l.getElementById(r[2]))&amp;&amp;s.parentNode){if(s.id!==r[2])return i.find(e);this.length=1,this[0]=s}return this.context=l,this.selector=e,this}return x.isFunction(e)?i.ready(e):(e.selector!==n&amp;&amp;(this.selector=e.selector,this.context=e.context),x.makeArray(e,this))},selector:"",jqx:"4.5.0",length:0,size:function(){return this.length},toArray:function(){return p.call(this)},get:function(e){return null==e?this.toArray():e&lt;0?this[this.length+e]:this[e]},pushStack:function(e,t,i){var r=x.merge(this.constructor(),e);return r.prevObject=this,r.context=this.context,"find"===t?r.selector=this.selector+(this.selector?" ":"")+i:t&amp;&amp;(r.selector=this.selector+"."+t+"("+i+")"),r},each:function(e,t){return x.each(this,e,t)},ready:function(e){return x.ready.promise().done(e),this},eq:function(e){return-1===(e=+e)?this.slice(e):this.slice(e,e+1)},first:function(){return this.eq(0)},last:function(){return this.eq(-1)},slice:function(){return this.pushStack(p.apply(this,arguments),"slice",p.call(arguments).join(","))},map:function(e){return this.pushStack(x.map(this,function(t,i){return e.call(t,i,t)}))},end:function(){return this.prevObject||this.constructor(null)},push:u,sort:[].sort,splice:[].splice},x.fn.init.prototype=x.fn,x.extend=x.fn.extend=function(){var e,t,i,r,s,o,a=arguments[0]||{},l=1,d=arguments.length,h=!1;for("boolean"==typeof a&amp;&amp;(h=a,a=arguments[1]||{},l=2),"object"==typeof a||x.isFunction(a)||(a={}),d===l&amp;&amp;(a=this,--l);l&lt;d;l++)if(null!=(e=arguments[l]))for(t in e)i=a[t],a!==(r=e[t])&amp;&amp;(h&amp;&amp;r&amp;&amp;(x.isPlainObject(r)||(s=x.isArray(r)))?(s?(s=!1,o=i&amp;&amp;x.isArray(i)?i:[]):o=i&amp;&amp;x.isPlainObject(i)?i:{},a[t]=x.extend(h,o,r)):r!==n&amp;&amp;(a[t]=r));return a},x.extend({noConflict:function(e){return s.$===x&amp;&amp;(s.$=c),e&amp;&amp;s.JQXLite===x&amp;&amp;(s.JQXLite=h),x},isReady:!1,readyWait:1,holdReady:function(e){e?x.readyWait++:x.ready(!0)},ready:function(e){if(!(!0===e?--x.readyWait:x.isReady)){if(!l.body)return setTimeout(x.ready,1);x.isReady=!0,!0!==e&amp;&amp;--x.readyWait&gt;0||(a.resolveWith(l,[x]),x.fn.trigger&amp;&amp;x(l).trigger("ready").off("ready"))}},isFunction:function(e){return"function"===x.type(e)},isArray:Array.isArray||function(e){return"array"===x.type(e)},isWindow:function(e){return null!=e&amp;&amp;e==e.window},isNumeric:function(e){return!isNaN(parseFloat(e))&amp;&amp;isFinite(e)},type:function(e){return null==e?String(e):M[f.call(e)]||"object"},isPlainObject:function(e){if(!e||"object"!==x.type(e)||e.nodeType||x.isWindow(e))return!1;try{if(e.constructor&amp;&amp;!g.call(e,"constructor")&amp;&amp;!g.call(e.constructor.prototype,"isPrototypeOf"))return!1}catch(e){return!1}var t;for(t in e);return t===n||g.call(e,t)},isEmptyObject:function(e){var t;for(t in e)return!1;return!0},error:function(e){throw new Error(e)},parseHTML:function(e,t,i){var r;return e&amp;&amp;"string"==typeof e?("boolean"==typeof t&amp;&amp;(i=t,t=0),t=t||l,(r=j.exec(e))?[t.createElement(r[1])]:(r=x.buildFragment([e],t,i?null:[]),x.merge([],(r.cacheable?x.clone(r.fragment):r.fragment).childNodes))):null},parseJSON:function(e){return e&amp;&amp;"string"==typeof e?(e=x.trim(e),s.JSON&amp;&amp;s.JSON.parse?s.JSON.parse(e):T.test(e.replace(S,"@").replace(k,"]").replace(C,""))?new Function("return "+e)():void x.error("Invalid JSON: "+e)):null},parseXML:function(e){var t;if(!e||"string"!=typeof e)return null;try{s.DOMParser?t=(new DOMParser).parseFromString(e,"text/xml"):((t=new ActiveXObject("Microsoft.XMLDOM")).async="false",t.loadXML(e))}catch(e){t=n}return t&amp;&amp;t.documentElement&amp;&amp;!t.getElementsByTagName("parsererror").length||x.error("Invalid XML: "+e),t},noop:function(){},globalEval:function(e){e&amp;&amp;w.test(e)&amp;&amp;(s.execScript||function(e){s.eval.call(s,e)})(e)},camelCase:function(e){return e.replace(I,"ms-").replace(D,P)},nodeName:function(e,t){return e.nodeName&amp;&amp;e.nodeName.toLowerCase()===t.toLowerCase()},each:function(e,t,i){var r,s=0,o=e.length,a=o===n||x.isFunction(e);if(i)if(a){for(r in e)if(!1===t.apply(e[r],i))break}else for(;s&lt;o&amp;&amp;!1!==t.apply(e[s++],i););else if(a){for(r in e)if(!1===t.call(e[r],r,e[r]))break}else for(;s&lt;o&amp;&amp;!1!==t.call(e[s],s,e[s++]););return e},trim:v&amp;&amp;!v.call("\ufeff ")?function(e){return null==e?"":v.call(e)}:function(e){return null==e?"":(e+"").replace(_,"")},makeArray:function(e,t){var i,r=t||[];return null!=e&amp;&amp;(i=x.type(e),null==e.length||"string"===i||"function"===i||"regexp"===i||x.isWindow(e)?u.call(r,e):x.merge(r,e)),r},inArray:function(e,t,i){var r;if(t){if(m)return m.call(t,e,i);for(r=t.length,i=i?i&lt;0?Math.max(0,r+i):i:0;i&lt;r;i++)if(i in t&amp;&amp;t[i]===e)return i}return-1},merge:function(e,t){var i=t.length,r=e.length,s=0;if("number"==typeof i)for(;s&lt;i;s++)e[r++]=t[s];else for(;t[s]!==n;)e[r++]=t[s++];return e.length=r,e},grep:function(e,t,i){var r=[],s=0,n=e.length;for(i=!!i;s&lt;n;s++)i!==!!t(e[s],s)&amp;&amp;r.push(e[s]);return r},map:function(e,t,i){var r,s,o=[],a=0,l=e.length;if(e instanceof x||l!==n&amp;&amp;"number"==typeof l&amp;&amp;(l&gt;0&amp;&amp;e[0]&amp;&amp;e[l-1]||0===l||x.isArray(e)))for(;a&lt;l;a++)null!=(r=t(e[a],a,i))&amp;&amp;(o[o.length]=r);else for(s in e)null!=(r=t(e[s],s,i))&amp;&amp;(o[o.length]=r);return o.concat.apply([],o)},guid:1,proxy:function(e,t){var i,r,s;return"string"==typeof t&amp;&amp;(i=e[t],t=e,e=i),x.isFunction(e)?(r=p.call(arguments,2),s=function(){return e.apply(t,r.concat(p.call(arguments)))},s.guid=e.guid=e.guid||x.guid++,s):n},access:function(e,t,i,r,s,o,a){var l,d=null==i,h=0,c=e.length;if(i&amp;&amp;"object"==typeof i){for(h in i)x.access(e,t,h,i[h],1,o,r);s=1}else if(r!==n){if(l=a===n&amp;&amp;x.isFunction(r),d&amp;&amp;(l?(l=t,t=function(e,t,i){return l.call(x(e),i)}):(t.call(e,r),t=null)),t)for(;h&lt;c;h++)t(e[h],i,l?r.call(e[h],h,t(e[h],i)):r,a);s=1}return s?e:d?t.call(e):c?t(e[0],i):o},now:function(){return(new Date).getTime()}}),x.ready.promise=function(e){if(!a)if(a=x.Deferred(),"complete"===l.readyState)setTimeout(x.ready,1);else if(l.addEventListener)l.addEventListener("DOMContentLoaded",A,!1),s.addEventListener("load",x.ready,!1);else{l.attachEvent("onreadystatechange",A),s.attachEvent("onload",x.ready);var t=!1;try{t=null==s.frameElement&amp;&amp;l.documentElement}catch(e){}t&amp;&amp;t.doScroll&amp;&amp;function e(){if(!x.isReady){try{t.doScroll("left")}catch(t){return setTimeout(e,50)}x.ready()}}()}return a.promise(e)},x.each("Boolean Number String Function Array Date RegExp Object".split(" "),function(e,t){M["[object "+t+"]"]=t.toLowerCase()}),o=x(l);var H={};x.Callbacks=function(e){e="string"==typeof e?H[e]||function(e){var t=H[e]={};return x.each(e.split(b),function(e,i){t[i]=!0}),t}(e):x.extend({},e);var t,i,r,s,o,a,l=[],d=!e.once&amp;&amp;[],h=function(n){for(t=e.memory&amp;&amp;n,i=!0,a=s||0,s=0,o=l.length,r=!0;l&amp;&amp;a&lt;o;a++)if(!1===l[a].apply(n[0],n[1])&amp;&amp;e.stopOnFalse){t=!1;break}r=!1,l&amp;&amp;(d?d.length&amp;&amp;h(d.shift()):t?l=[]:c.disable())},c={add:function(){if(l){var i=l.length;!function t(i){x.each(i,function(i,r){var s=x.type(r);"function"===s?e.unique&amp;&amp;c.has(r)||l.push(r):r&amp;&amp;r.length&amp;&amp;"string"!==s&amp;&amp;t(r)})}(arguments),r?o=l.length:t&amp;&amp;(s=i,h(t))}return this},remove:function(){return l&amp;&amp;x.each(arguments,function(e,t){for(var i;(i=x.inArray(t,l,i))&gt;-1;)l.splice(i,1),r&amp;&amp;(i&lt;=o&amp;&amp;o--,i&lt;=a&amp;&amp;a--)}),this},has:function(e){return x.inArray(e,l)&gt;-1},empty:function(){return l=[],this},disable:function(){return l=d=t=n,this},disabled:function(){return!l},lock:function(){return d=n,t||c.disable(),this},locked:function(){return!d},fireWith:function(e,t){return t=[e,(t=t||[]).slice?t.slice():t],!l||i&amp;&amp;!d||(r?d.push(t):h(t)),this},fire:function(){return c.fireWith(this,arguments),this},fired:function(){return!!i}};return c},x.extend({Deferred:function(e){var t=[["resolve","done",x.Callbacks("once memory"),"resolved"],["reject","fail",x.Callbacks("once memory"),"rejected"],["notify","progress",x.Callbacks("memory")]],i="pending",r={state:function(){return i},always:function(){return s.done(arguments).fail(arguments),this},then:function(){var e=arguments;return x.Deferred(function(i){x.each(t,function(t,r){var n=r[0],o=e[t];s[r[1]](x.isFunction(o)?function(){var e=o.apply(this,arguments);e&amp;&amp;x.isFunction(e.promise)?e.promise().done(i.resolve).fail(i.reject).progress(i.notify):i[n+"With"](this===s?i:this,[e])}:i[n])}),e=null}).promise()},promise:function(e){return null!=e?x.extend(e,r):r}},s={};return r.pipe=r.then,x.each(t,function(e,n){var o=n[2],a=n[3];r[n[1]]=o.add,a&amp;&amp;o.add(function(){i=a},t[1^e][2].disable,t[2][2].lock),s[n[0]]=o.fire,s[n[0]+"With"]=o.fireWith}),r.promise(s),e&amp;&amp;e.call(s,s),s},when:function(e){var t,i,r,s=0,n=p.call(arguments),o=n.length,a=1!==o||e&amp;&amp;x.isFunction(e.promise)?o:0,l=1===a?e:x.Deferred(),d=function(e,i,r){return function(s){i[e]=this,r[e]=arguments.length&gt;1?p.call(arguments):s,r===t?l.notifyWith(i,r):--a||l.resolveWith(i,r)}};if(o&gt;1)for(t=new Array(o),i=new Array(o),r=new Array(o);s&lt;o;s++)n[s]&amp;&amp;x.isFunction(n[s].promise)?n[s].promise().done(d(s,r,n)).fail(l.reject).progress(d(s,i,t)):--a;return a||l.resolveWith(r,n),l.promise()}}),x.support=function(){var e,t,i,r,n,o,a,d,h,c,u,p=l.createElement("div");if(p.setAttribute("className","t"),p.innerHTML="  &lt;link/&gt;&lt;table&gt;&lt;/table&gt;&lt;a href='/a'&gt;a&lt;/a&gt;&lt;input type='checkbox'/&gt;",t=p.getElementsByTagName("*"),i=p.getElementsByTagName("a")[0],!t||!i||!t.length)return{};n=(r=l.createElement("select")).appendChild(l.createElement("option")),o=p.getElementsByTagName("input")[0],i.style.cssText="top:1px;float:left;opacity:.5",e={leadingWhitespace:3===p.firstChild.nodeType,tbody:!p.getElementsByTagName("tbody").length,htmlSerialize:!!p.getElementsByTagName("link").length,style:/top/.test(i.getAttribute("style")),hrefNormalized:"/a"===i.getAttribute("href"),opacity:/^0.5/.test(i.style.opacity),cssFloat:!!i.style.cssFloat,checkOn:"on"===o.value,optSelected:n.selected,getSetAttribute:"t"!==p.className,enctype:!!l.createElement("form").enctype,html5Clone:"&lt;:nav&gt;&lt;/:nav&gt;"!==l.createElement("nav").cloneNode(!0).outerHTML,boxModel:"CSS1Compat"===l.compatMode,submitBubbles:!0,changeBubbles:!0,focusinBubbles:!1,deleteExpando:!0,noCloneEvent:!0,inlineBlockNeedsLayout:!1,shrinkWrapBlocks:!1,reliableMarginRight:!0,boxSizingReliable:!0,pixelPosition:!1},o.checked=!0,e.noCloneChecked=o.cloneNode(!0).checked,r.disabled=!0,e.optDisabled=!n.disabled;try{delete p.test}catch(t){e.deleteExpando=!1}if(!p.addEventListener&amp;&amp;p.attachEvent&amp;&amp;p.fireEvent&amp;&amp;(p.attachEvent("onclick",u=function(){e.noCloneEvent=!1}),p.cloneNode(!0).fireEvent("onclick"),p.detachEvent("onclick",u)),(o=l.createElement("input")).value="t",o.setAttribute("type","radio"),e.radioValue="t"===o.value,o.setAttribute("checked","checked"),o.setAttribute("name","t"),p.appendChild(o),(a=l.createDocumentFragment()).appendChild(p.lastChild),e.checkClone=a.cloneNode(!0).cloneNode(!0).lastChild.checked,e.appendChecked=o.checked,a.removeChild(o),a.appendChild(p),p.attachEvent)for(h in{submit:!0,change:!0,focusin:!0})(c=(d="on"+h)in p)||(p.setAttribute(d,"return;"),c="function"==typeof p[d]),e[h+"Bubbles"]=c;return x(function(){var t,i,r,n,o="padding:0;margin:0;border:0;display:block;overflow:hidden;",a=l.getElementsByTagName("body")[0];a&amp;&amp;((t=l.createElement("div")).style.cssText="visibility:hidden;border:0;width:0;height:0;position:static;top:0;margin-top:1px",a.insertBefore(t,a.firstChild),i=l.createElement("div"),t.appendChild(i),i.innerHTML="&lt;table&gt;&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;t&lt;/td&gt;&lt;/tr&gt;&lt;/table&gt;",(r=i.getElementsByTagName("td"))[0].style.cssText="padding:0;margin:0;border:0;display:none",c=0===r[0].offsetHeight,r[0].style.display="",r[1].style.display="none",e.reliableHiddenOffsets=c&amp;&amp;0===r[0].offsetHeight,i.innerHTML="",i.style.cssText="box-sizing:border-box;-moz-box-sizing:border-box;-webkit-box-sizing:border-box;padding:1px;border:1px;display:block;width:4px;margin-top:1%;position:absolute;top:1%;",e.boxSizing=4===i.offsetWidth,e.doesNotIncludeMarginInBodyOffset=1!==a.offsetTop,s.getComputedStyle&amp;&amp;(e.pixelPosition="1%"!==(s.getComputedStyle(i,null)||{}).top,e.boxSizingReliable="4px"===(s.getComputedStyle(i,null)||{width:"4px"}).width,(n=l.createElement("div")).style.cssText=i.style.cssText=o,n.style.marginRight=n.style.width="0",i.style.width="1px",i.appendChild(n),e.reliableMarginRight=!parseFloat((s.getComputedStyle(n,null)||{}).marginRight)),void 0!==i.style.zoom&amp;&amp;(i.innerHTML="",i.style.cssText=o+"width:1px;padding:1px;display:inline;zoom:1",e.inlineBlockNeedsLayout=3===i.offsetWidth,i.style.display="block",i.style.overflow="visible",i.innerHTML="&lt;div&gt;&lt;/div&gt;",i.firstChild.style.width="5px",e.shrinkWrapBlocks=3!==i.offsetWidth,t.style.zoom=1),a.removeChild(t),t=i=r=n=null)}),a.removeChild(p),t=i=r=n=o=a=p=null,e}();var B=/(?:\{[\s\S]*\}|\[[\s\S]*\])$/,z=/([A-Z])/g;function E(e,t,i){if(i===n&amp;&amp;1===e.nodeType){var r="data-"+t.replace(z,"-$1").toLowerCase();if("string"==typeof(i=e.getAttribute(r))){try{i="true"===i||"false"!==i&amp;&amp;("null"===i?null:+i+""===i?+i:B.test(i)?x.parseJSON(i):i)}catch(e){}x.data(e,t,i)}else i=n}return i}function L(e){var t;for(t in e)if(("data"!==t||!x.isEmptyObject(e[t]))&amp;&amp;"toJSON"!==t)return!1;return!0}x.extend({cache:{},deletedIds:[],uuid:0,expando:"JQXLite"+(x.fn.jqx+Math.random()).replace(/\D/g,""),noData:{embed:!0,object:"clsid:D27CDB6E-AE6D-11cf-96B8-444553540000",applet:!0},hasData:function(e){return!!(e=e.nodeType?x.cache[e[x.expando]]:e[x.expando])&amp;&amp;!L(e)},data:function(e,t,i,r){if(x.acceptData(e)){var s,o,a=x.expando,l="string"==typeof t,d=e.nodeType,h=d?x.cache:e,c=d?e[a]:e[a]&amp;&amp;a;if(c&amp;&amp;h[c]&amp;&amp;(r||h[c].data)||!l||i!==n)return c||(d?e[a]=c=x.deletedIds.pop()||x.guid++:c=a),h[c]||(h[c]={},d||(h[c].toJSON=x.noop)),"object"!=typeof t&amp;&amp;"function"!=typeof t||(r?h[c]=x.extend(h[c],t):h[c].data=x.extend(h[c].data,t)),s=h[c],r||(s.data||(s.data={}),s=s.data),i!==n&amp;&amp;(s[x.camelCase(t)]=i),l?null==(o=s[t])&amp;&amp;(o=s[x.camelCase(t)]):o=s,o}},removeData:function(e,t,i){if(x.acceptData(e)){var r,s,n,o=e.nodeType,a=o?x.cache:e,l=o?e[x.expando]:x.expando;if(a[l]){if(t&amp;&amp;(r=i?a[l]:a[l].data)){x.isArray(t)||(t=t in r||(t=x.camelCase(t))in r?[t]:t.split(" "));for(s=0,n=t.length;s&lt;n;s++)delete r[t[s]];if(!(i?L:x.isEmptyObject)(r))return}(i||(delete a[l].data,L(a[l])))&amp;&amp;(o?x.cleanData([e],!0):x.support.deleteExpando||a!=a.window?delete a[l]:a[l]=null)}}},_data:function(e,t,i){return x.data(e,t,i,!0)},acceptData:function(e){var t=e.nodeName&amp;&amp;x.noData[e.nodeName.toLowerCase()];return!t||!0!==t&amp;&amp;e.getAttribute("classid")===t}}),x.fn.extend({data:function(e,t){var i,r,s,o,a,l=this[0],d=0,h=null;if(e===n){if(this.length&amp;&amp;(h=x.data(l),1===l.nodeType&amp;&amp;!x._data(l,"parsedAttrs"))){for(a=(s=l.attributes).length;d&lt;a;d++)(o=s[d].name).indexOf("data-")||(o=x.camelCase(o.substring(5)),E(l,o,h[o]));x._data(l,"parsedAttrs",!0)}return h}return"object"==typeof e?this.each(function(){x.data(this,e)}):((i=e.split(".",2))[1]=i[1]?"."+i[1]:"",r=i[1]+"!",x.access(this,function(t){if(t===n)return(h=this.triggerHandler("getData"+r,[i[0]]))===n&amp;&amp;l&amp;&amp;(h=x.data(l,e),h=E(l,e,h)),h===n&amp;&amp;i[1]?this.data(i[0]):h;i[1]=t,this.each(function(){var s=x(this);s.triggerHandler("setData"+r,i),x.data(this,e,t),s.triggerHandler("changeData"+r,i)})},null,t,arguments.length&gt;1,null,!1))},removeData:function(e){return this.each(function(){x.removeData(this,e)})}}),x.extend({queue:function(e,t,i){var r;if(e)return t=(t||"fx")+"queue",r=x._data(e,t),i&amp;&amp;(!r||x.isArray(i)?r=x._data(e,t,x.makeArray(i)):r.push(i)),r||[]},dequeue:function(e,t){t=t||"fx";var i=x.queue(e,t),r=i.length,s=i.shift(),n=x._queueHooks(e,t);"inprogress"===s&amp;&amp;(s=i.shift(),r--),s&amp;&amp;("fx"===t&amp;&amp;i.unshift("inprogress"),delete n.stop,s.call(e,function(){x.dequeue(e,t)},n)),!r&amp;&amp;n&amp;&amp;n.empty.fire()},_queueHooks:function(e,t){var i=t+"queueHooks";return x._data(e,i)||x._data(e,i,{empty:x.Callbacks("once memory").add(function(){x.removeData(e,t+"queue",!0),x.removeData(e,i,!0)})})}}),x.fn.extend({queue:function(e,t){var i=2;return"string"!=typeof e&amp;&amp;(t=e,e="fx",i--),arguments.length&lt;i?x.queue(this[0],e):t===n?this:this.each(function(){var i=x.queue(this,e,t);x._queueHooks(this,e),"fx"===e&amp;&amp;"inprogress"!==i[0]&amp;&amp;x.dequeue(this,e)})},dequeue:function(e){return this.each(function(){x.dequeue(this,e)})},delay:function(e,t){return e=x.fx&amp;&amp;x.fx.speeds[e]||e,t=t||"fx",this.queue(t,function(t,i){var r=setTimeout(t,e);i.stop=function(){clearTimeout(r)}})},clearQueue:function(e){return this.queue(e||"fx",[])},promise:function(e,t){var i,r=1,s=x.Deferred(),o=this,a=this.length,l=function(){--r||s.resolveWith(o,[o])};for("string"!=typeof e&amp;&amp;(t=e,e=n),e=e||"fx";a--;)(i=x._data(o[a],e+"queueHooks"))&amp;&amp;i.empty&amp;&amp;(r++,i.empty.add(l));return l(),s.promise(t)}});var N,O=/[\t\r\n]/g,R=/\r/g,F=/^(?:button|input)$/i,W=/^(?:button|input|object|select|textarea)$/i,V=/^a(?:rea|)$/i,G=/^(?:autofocus|autoplay|async|checked|controls|defer|disabled|hidden|loop|multiple|open|readonly|required|scoped|selected)$/i,U=x.support.getSetAttribute;x.fn.extend({attr:function(e,t){return x.access(this,x.attr,e,t,arguments.length&gt;1)},removeAttr:function(e){return this.each(function(){x.removeAttr(this,e)})},prop:function(e,t){return x.access(this,x.prop,e,t,arguments.length&gt;1)},removeProp:function(e){return e=x.propFix[e]||e,this.each(function(){try{this[e]=n,delete this[e]}catch(e){}})},addClass:function(e){var t,i,r,s,n,o,a;if(x.isFunction(e))return this.each(function(t){x(this).addClass(e.call(this,t,this.className))});if(e&amp;&amp;"string"==typeof e)for(t=e.split(b),i=0,r=this.length;i&lt;r;i++)if(1===(s=this[i]).nodeType)if(s.className||1!==t.length){for(n=" "+s.className+" ",o=0,a=t.length;o&lt;a;o++)n.indexOf(" "+t[o]+" ")&lt;0&amp;&amp;(n+=t[o]+" ");s.className=x.trim(n)}else s.className=e;return this},removeClass:function(e){var t,i,r,s,o,a,l;if(x.isFunction(e))return this.each(function(t){x(this).removeClass(e.call(this,t,this.className))});if(e&amp;&amp;"string"==typeof e||e===n)for(t=(e||"").split(b),a=0,l=this.length;a&lt;l;a++)if(1===(r=this[a]).nodeType&amp;&amp;r.className){for(i=(" "+r.className+" ").replace(O," "),s=0,o=t.length;s&lt;o;s++)for(;i.indexOf(" "+t[s]+" ")&gt;=0;)i=i.replace(" "+t[s]+" "," ");r.className=e?x.trim(i):""}return this},toggleClass:function(e,t){var i=typeof e,r="boolean"==typeof t;return x.isFunction(e)?this.each(function(i){x(this).toggleClass(e.call(this,i,this.className,t),t)}):this.each(function(){if("string"===i)for(var s,n=0,o=x(this),a=t,l=e.split(b);s=l[n++];)a=r?a:!o.hasClass(s),o[a?"addClass":"removeClass"](s);else"undefined"!==i&amp;&amp;"boolean"!==i||(this.className&amp;&amp;x._data(this,"__className__",this.className),this.className=this.className||!1===e?"":x._data(this,"__className__")||"")})},hasClass:function(e){for(var t=" "+e+" ",i=0,r=this.length;i&lt;r;i++)if(1===this[i].nodeType&amp;&amp;(" "+this[i].className+" ").replace(O," ").indexOf(t)&gt;=0)return!0;return!1},val:function(e){var t,i,r,s=this[0];return arguments.length?(r=x.isFunction(e),this.each(function(i){var s,o=x(this);1===this.nodeType&amp;&amp;(null==(s=r?e.call(this,i,o.val()):e)?s="":"number"==typeof s?s+="":x.isArray(s)&amp;&amp;(s=x.map(s,function(e){return null==e?"":e+""})),(t=x.valHooks[this.type]||x.valHooks[this.nodeName.toLowerCase()])&amp;&amp;"set"in t&amp;&amp;t.set(this,s,"value")!==n||(this.value=s))})):s?(t=x.valHooks[s.type]||x.valHooks[s.nodeName.toLowerCase()])&amp;&amp;"get"in t&amp;&amp;(i=t.get(s,"value"))!==n?i:"string"==typeof(i=s.value)?i.replace(R,""):null==i?"":i:void 0}}),x.extend({valHooks:{option:{get:function(e){var t=e.attributes.value;return!t||t.specified?e.value:e.text}},select:{get:function(e){for(var t,i,r=e.options,s=e.selectedIndex,n="select-one"===e.type||s&lt;0,o=n?null:[],a=n?s+1:r.length,l=s&lt;0?a:n?s:0;l&lt;a;l++)if(((i=r[l]).selected||l===s)&amp;&amp;(x.support.optDisabled?!i.disabled:null===i.getAttribute("disabled"))&amp;&amp;(!i.parentNode.disabled||!x.nodeName(i.parentNode,"optgroup"))){if(t=x(i).val(),n)return t;o.push(t)}return o},set:function(e,t){var i=x.makeArray(t);return x(e).find("option").each(function(){this.selected=x.inArray(x(this).val(),i)&gt;=0}),i.length||(e.selectedIndex=-1),i}}},attrFn:{},attr:function(e,t,i,r){var s,o,a,l=e.nodeType;if(e&amp;&amp;3!==l&amp;&amp;8!==l&amp;&amp;2!==l)return r&amp;&amp;x.isFunction(x.fn[t])?x(e)[t](i):void 0===e.getAttribute?x.prop(e,t,i):((a=1!==l||!x.isXMLDoc(e))&amp;&amp;(t=t.toLowerCase(),o=x.attrHooks[t]||(G.test(t)?N:undefined)),i!==n?null===i?void x.removeAttr(e,t):o&amp;&amp;"set"in o&amp;&amp;a&amp;&amp;(s=o.set(e,i,t))!==n?s:(e.setAttribute(t,i+""),i):o&amp;&amp;"get"in o&amp;&amp;a&amp;&amp;null!==(s=o.get(e,t))?s:null===(s=e.getAttribute(t))?n:s)},removeAttr:function(e,t){var i,r,s,n,o=0;if(t&amp;&amp;1===e.nodeType)for(r=t.split(b);o&lt;r.length;o++)(s=r[o])&amp;&amp;(i=x.propFix[s]||s,(n=G.test(s))||x.attr(e,s,""),e.removeAttribute(U?s:i),n&amp;&amp;i in e&amp;&amp;(e[i]=!1))},attrHooks:{type:{set:function(e,t){if(F.test(e.nodeName)&amp;&amp;e.parentNode)x.error("type property can't be changed");else if(!x.support.radioValue&amp;&amp;"radio"===t&amp;&amp;x.nodeName(e,"input")){var i=e.value;return e.setAttribute("type",t),i&amp;&amp;(e.value=i),t}}},value:{get:function(e,t){return t in e?e.value:null},set:function(e,t,i){e.value=t}}},propFix:{tabindex:"tabIndex",readonly:"readOnly",for:"htmlFor",class:"className",maxlength:"maxLength",cellspacing:"cellSpacing",cellpadding:"cellPadding",rowspan:"rowSpan",colspan:"colSpan",usemap:"useMap",frameborder:"frameBorder",contenteditable:"contentEditable"},prop:function(e,t,i){var r,s,o=e.nodeType;if(e&amp;&amp;3!==o&amp;&amp;8!==o&amp;&amp;2!==o)return(1!==o||!x.isXMLDoc(e))&amp;&amp;(t=x.propFix[t]||t,s=x.propHooks[t]),i!==n?s&amp;&amp;"set"in s&amp;&amp;(r=s.set(e,i,t))!==n?r:e[t]=i:s&amp;&amp;"get"in s&amp;&amp;null!==(r=s.get(e,t))?r:e[t]},propHooks:{tabIndex:{get:function(e){var t=e.getAttributeNode("tabindex");return t&amp;&amp;t.specified?parseInt(t.value,10):W.test(e.nodeName)||V.test(e.nodeName)&amp;&amp;e.href?0:n}}}}),N={get:function(e,t){var i,r=x.prop(e,t);return!0===r||"boolean"!=typeof r&amp;&amp;(i=e.getAttributeNode(t))&amp;&amp;!1!==i.nodeValue?t.toLowerCase():n},set:function(e,t,i){var r;return!1===t?x.removeAttr(e,i):((r=x.propFix[i]||i)in e&amp;&amp;(e[r]=!0),e.setAttribute(i,i.toLowerCase())),i}},x.support.enctype||(x.propFix.enctype="encoding");var Y=/^([^\.]*|)(?:\.(.+)|)$/,K=/(?:^|\s)hover(\.\S+|)\b/,X=/^key/,Z=/^(?:mouse|contextmenu)|click/,$=/^(?:focusinfocus|focusoutblur)$/,J=function(e){return x.event.special.hover?e:e.replace(K,"mouseenter$1 mouseleave$1")};function Q(){return!1}function ee(){return!0}x.event={add:function(e,t,i,r,s){var o,a,l,d,h,c,u,p,m,f,g;if(3!==e.nodeType&amp;&amp;8!==e.nodeType&amp;&amp;t&amp;&amp;i&amp;&amp;(o=x._data(e))){for(i.handler&amp;&amp;(i=(m=i).handler,s=m.selector),i.guid||(i.guid=x.guid++),(l=o.events)||(o.events=l={}),(a=o.handle)||(o.handle=a=function(e){return void 0===x||e&amp;&amp;x.event.triggered===e.type?n:x.event.dispatch.apply(a.elem,arguments)},a.elem=e),t=x.trim(J(t)).split(" "),d=0;d&lt;t.length;d++)c=(h=Y.exec(t[d])||[])[1],u=(h[2]||"").split(".").sort(),g=x.event.special[c]||{},c=(s?g.delegateType:g.bindType)||c,g=x.event.special[c]||{},p=x.extend({type:c,origType:h[1],data:r,handler:i,guid:i.guid,selector:s,needsContext:s&amp;&amp;x.expr.match.needsContext.test(s),namespace:u.join(".")},m),(f=l[c])||((f=l[c]=[]).delegateCount=0,g.setup&amp;&amp;!1!==g.setup.call(e,r,u,a)||(e.addEventListener?r&amp;&amp;r.passive!==n?e.addEventListener(c,a,r):e.addEventListener(c,a,!1):e.attachEvent&amp;&amp;e.attachEvent("on"+c,a))),g.add&amp;&amp;(g.add.call(e,p),p.handler.guid||(p.handler.guid=i.guid)),s?f.splice(f.delegateCount++,0,p):f.push(p),x.event.global[c]=!0;e=null}},global:{},remove:function(e,t,i,r,s){var n,o,a,l,d,h,c,u,p,m,f,g=x.hasData(e)&amp;&amp;x._data(e);if(g&amp;&amp;(u=g.events)){for(t=x.trim(J(t||"")).split(" "),n=0;n&lt;t.length;n++)if(a=l=(o=Y.exec(t[n])||[])[1],d=o[2],a){for(p=x.event.special[a]||{},h=(m=u[a=(r?p.delegateType:p.bindType)||a]||[]).length,d=d?new RegExp("(^|\\.)"+d.split(".").sort().join("\\.(?:.*\\.|)")+"(\\.|$)"):null,c=0;c&lt;m.length;c++)f=m[c],!s&amp;&amp;l!==f.origType||i&amp;&amp;i.guid!==f.guid||d&amp;&amp;!d.test(f.namespace)||r&amp;&amp;r!==f.selector&amp;&amp;("**"!==r||!f.selector)||(m.splice(c--,1),f.selector&amp;&amp;m.delegateCount--,p.remove&amp;&amp;p.remove.call(e,f));0===m.length&amp;&amp;h!==m.length&amp;&amp;(p.teardown&amp;&amp;!1!==p.teardown.call(e,d,g.handle)||x.removeEvent(e,a,g.handle),delete u[a])}else for(a in u)x.event.remove(e,a+t[n],i,r,!0);x.isEmptyObject(u)&amp;&amp;(delete g.handle,x.removeData(e,"events",!0))}},customEvent:{getData:!0,setData:!0,changeData:!0},trigger:function(e,t,i,r){if(!i||3!==i.nodeType&amp;&amp;8!==i.nodeType){var o,a,d,h,c,u,p,m,f,g,v=e.type||e,y=[];if(!$.test(v+x.event.triggered)&amp;&amp;(v.indexOf("!")&gt;=0&amp;&amp;(v=v.slice(0,-1),a=!0),v.indexOf(".")&gt;=0&amp;&amp;(y=v.split("."),v=y.shift(),y.sort()),i&amp;&amp;!x.event.customEvent[v]||x.event.global[v]))if((e="object"==typeof e?e[x.expando]?e:new x.Event(v,e):new x.Event(v)).type=v,e.isTrigger=!0,e.exclusive=a,e.namespace=y.join("."),e.namespace_re=e.namespace?new RegExp("(^|\\.)"+y.join("\\.(?:.*\\.|)")+"(\\.|$)"):null,u=v.indexOf(":")&lt;0?"on"+v:"",i){if(e.result=n,e.target||(e.target=i),(t=null!=t?x.makeArray(t):[]).unshift(e),!(p=x.event.special[v]||{}).trigger||!1!==p.trigger.apply(i,t)){if(f=[[i,p.bindType||v]],!r&amp;&amp;!p.noBubble&amp;&amp;!x.isWindow(i)){for(g=p.delegateType||v,h=$.test(g+v)?i:i.parentNode,c=i;h;h=h.parentNode)f.push([h,g]),c=h;c===(i.ownerDocument||l)&amp;&amp;f.push([c.defaultView||c.parentWindow||s,g])}for(d=0;d&lt;f.length&amp;&amp;!e.isPropagationStopped();d++)h=f[d][0],e.type=f[d][1],(m=(x._data(h,"events")||{})[e.type]&amp;&amp;x._data(h,"handle"))&amp;&amp;m.apply(h,t),(m=u&amp;&amp;h[u])&amp;&amp;x.acceptData(h)&amp;&amp;m.apply&amp;&amp;!1===m.apply(h,t)&amp;&amp;e.preventDefault();return e.type=v,r||e.isDefaultPrevented()||p._default&amp;&amp;!1!==p._default.apply(i.ownerDocument,t)||"click"===v&amp;&amp;x.nodeName(i,"a")||!x.acceptData(i)||u&amp;&amp;i[v]&amp;&amp;("focus"!==v&amp;&amp;"blur"!==v||0!==e.target.offsetWidth)&amp;&amp;!x.isWindow(i)&amp;&amp;((c=i[u])&amp;&amp;(i[u]=null),x.event.triggered=v,i[v](),x.event.triggered=n,c&amp;&amp;(i[u]=c)),e.result}}else for(d in o=x.cache)o[d].events&amp;&amp;o[d].events[v]&amp;&amp;x.event.trigger(e,t,o[d].handle.elem,!0)}},dispatch:function(e){e=x.event.fix(e||s.event);var t,i,r,o,a,l,d,h,c,u=(x._data(this,"events")||{})[e.type]||[],m=u.delegateCount,f=p.call(arguments),g=!e.exclusive&amp;&amp;!e.namespace,v=x.event.special[e.type]||{},y=[];if(f[0]=e,e.delegateTarget=this,!v.preDispatch||!1!==v.preDispatch.call(this,e)){if(m&amp;&amp;(!e.button||"click"!==e.type))for(r=e.target;r!=this;r=r.parentNode||this)if(!0!==r.disabled||"click"!==e.type){for(a={},d=[],t=0;t&lt;m;t++)a[c=(h=u[t]).selector]===n&amp;&amp;(a[c]=h.needsContext?x(c,this).index(r)&gt;=0:x.find(c,this,null,[r]).length),a[c]&amp;&amp;d.push(h);d.length&amp;&amp;y.push({elem:r,matches:d})}for(u.length&gt;m&amp;&amp;y.push({elem:this,matches:u.slice(m)}),t=0;t&lt;y.length&amp;&amp;!e.isPropagationStopped();t++)for(l=y[t],e.currentTarget=l.elem,i=0;i&lt;l.matches.length&amp;&amp;!e.isImmediatePropagationStopped();i++)h=l.matches[i],(g||!e.namespace&amp;&amp;!h.namespace||e.namespace_re&amp;&amp;e.namespace_re.test(h.namespace))&amp;&amp;(e.data=h.data,e.handleObj=h,(o=((x.event.special[h.origType]||{}).handle||h.handler).apply(l.elem,f))!==n&amp;&amp;(e.result=o,!1===o&amp;&amp;(e.preventDefault(),e.stopPropagation())));return v.postDispatch&amp;&amp;v.postDispatch.call(this,e),e.result}},props:"attrChange attrName relatedNode srcElement altKey bubbles cancelable ctrlKey currentTarget eventPhase metaKey relatedTarget shiftKey target timeStamp view which".split(" "),fixHooks:{},keyHooks:{props:"char charCode key keyCode".split(" "),filter:function(e,t){return null==e.which&amp;&amp;(e.which=null!=t.charCode?t.charCode:t.keyCode),e}},mouseHooks:{props:"button buttons clientX clientY fromElement offsetX offsetY pageX pageY screenX screenY toElement".split(" "),filter:function(e,t){var i,r,s,o=t.button,a=t.fromElement;return null==e.pageX&amp;&amp;null!=t.clientX&amp;&amp;(r=(i=e.target.ownerDocument||l).documentElement,s=i.body,e.pageX=t.clientX+(r&amp;&amp;r.scrollLeft||s&amp;&amp;s.scrollLeft||0)-(r&amp;&amp;r.clientLeft||s&amp;&amp;s.clientLeft||0),e.pageY=t.clientY+(r&amp;&amp;r.scrollTop||s&amp;&amp;s.scrollTop||0)-(r&amp;&amp;r.clientTop||s&amp;&amp;s.clientTop||0)),!e.relatedTarget&amp;&amp;a&amp;&amp;(e.relatedTarget=a===e.target?t.toElement:a),e.which||o===n||(e.which=1&amp;o?1:2&amp;o?3:4&amp;o?2:0),e}},fix:function(e){if(e[x.expando])return e;var t,i,r=e,s=x.event.fixHooks[e.type]||{},n=s.props?this.props.concat(s.props):this.props;for(e=x.Event(r),t=n.length;t;)e[i=n[--t]]=r[i];return e.target||(e.target=r.srcElement||l),3===e.target.nodeType&amp;&amp;(e.target=e.target.parentNode),e.metaKey=!!e.metaKey,s.filter?s.filter(e,r):e},special:{load:{noBubble:!0},focus:{delegateType:"focusin"},blur:{delegateType:"focusout"},beforeunload:{setup:function(e,t,i){x.isWindow(this)&amp;&amp;(this.onbeforeunload=i)},teardown:function(e,t){this.onbeforeunload===t&amp;&amp;(this.onbeforeunload=null)}}},simulate:function(e,t,i,r){var s=x.extend(new x.Event,i,{type:e,isSimulated:!0,originalEvent:{}});r?x.event.trigger(s,null,t):x.event.dispatch.call(t,s),s.isDefaultPrevented()&amp;&amp;i.preventDefault()}},x.event.handle=x.event.dispatch,x.removeEvent=l.removeEventListener?function(e,t,i){e.removeEventListener&amp;&amp;e.removeEventListener(t,i,!1)}:function(e,t,i){var r="on"+t;e.detachEvent&amp;&amp;(void 0===e[r]&amp;&amp;(e[r]=null),e.detachEvent(r,i))},x.Event=function(e,t){if(!(this instanceof x.Event))return new x.Event(e,t);e&amp;&amp;e.type?(this.originalEvent=e,this.type=e.type,this.isDefaultPrevented=e.defaultPrevented||!1===e.returnValue||e.getPreventDefault&amp;&amp;e.getPreventDefault()?ee:Q):this.type=e,t&amp;&amp;x.extend(this,t),this.timeStamp=e&amp;&amp;e.timeStamp||x.now(),this[x.expando]=!0},x.Event.prototype={preventDefault:function(){this.isDefault</t>
+  </si>
+  <si>
+    <t>https://jqwidgets.com/export_server/dataexport.php</t>
+  </si>
+  <si>
+    <t>u00ad</t>
+  </si>
+  <si>
+    <t>verified_from_local_source_candidate</t>
+  </si>
+  <si>
+    <t>Auto-promoted only because source file, phone, url, postcode, and company-like source line were present. Still recommended for human review before DB import.</t>
+  </si>
+  <si>
+    <t>C:\AAYS_GITHUB_BRIDGE_CLEAN2\ai-data\ty150-nista-pipeline-deep-discovery\raw\https___pipeline.nista.grid.civilservice.gov.uk_assets_jqx-all.js_m_1773333865.0.txt</t>
+  </si>
+  <si>
+    <t>EA-REVIEW-EA-CAND-000023</t>
+  </si>
+  <si>
+    <t>EA-CAND-000023</t>
+  </si>
+  <si>
+    <t>!function(){var e,t,n={14296:function(e,t,n){var r;window,e.exports=(r=n(51609),function(e){var t={};function n(r){if(t[r])return t[r].exports;var a=t[r]={i:r,l:!1,exports:{}};return e[r].call(a.exports,a,a.exports,n),a.l=!0,a.exports}return n.m=e,n.c=t,n.d=function(e,t,r){n.o(e,t)||Object.defineProperty(e,t,{enumerable:!0,get:r})},n.r=function(e){"undefined"!=typeof Symbol&amp;&amp;Symbol.toStringTag&amp;&amp;Object.defineProperty(e,Symbol.toStringTag,{value:"Module"}),Object.defineProperty(e,"__esModule",{value:!0})},n.t=function(e,t){if(1&amp;t&amp;&amp;(e=n(e)),8&amp;t)return e;if(4&amp;t&amp;&amp;"object"==typeof e&amp;&amp;e&amp;&amp;e.__esModule)return e;var r=Object.create(null);if(n.r(r),Object.defineProperty(r,"default",{enumerable:!0,value:e}),2&amp;t&amp;&amp;"string"!=typeof e)for(var a in e)n.d(r,a,function(t){return e[t]}.bind(null,a));return r},n.n=function(e){var t=e&amp;&amp;e.__esModule?function(){return e.default}:function(){return e};return n.d(t,"a",t),t},n.o=function(e,t){return Object.prototype.hasOwnProperty.call(e,t)},n.p="",n(n.s=1)}([function(e,t){e.exports=r},function(e,t,n){"use strict";n.r(t),n.d(t,"asyncDecorator",(function(){return i})),n.d(t,"inheritAsyncDecorator",(function(){return s})),n.d(t,"isReady",(function(){return l})),n.d(t,"History",(function(){return d}));var r=n(0);function a(e,t,n,r,a,o,i){try{var s=e[o](i),l=s.value}catch(e){return void n(e)}s.done?t(l):Promise.resolve(l).then(r,a)}function o(e){return function(){var t=this,n=arguments;return new Promise((function(r,o){var i=e.apply(t,n);function s(e){a(i,r,o,s,l,"next",e)}function l(e){a(i,r,o,s,l,"throw",e)}s(void 0)}))}}var i=function(e,t){var n,a={isReady:new Promise((function(e){n=e})),get:Object(r.lazy)((function(){return Promise.resolve(t()).then((function(e){return setTimeout(o(regeneratorRuntime.mark((function e(){return regeneratorRuntime.wrap((function(e){for(;;)switch(e.prev=e.next){case 0:return e.next=2,n(!0);case 2:a.isReady=!0;case 3:case"end":return e.stop()}}),e)}))),0),e}))}))};return Object.defineProperty(e,"_dashprivate_isLazyComponentReady",{get:function(){return a.isReady}}),a.get},s=function(e,t){Object.defineProperty(e,"_dashprivate_isLazyComponentReady",{get:function(){return l(t)}})},l=function(e){return e&amp;&amp;e._dashprivate_isLazyComponentReady};function c(e,t){for(var n=0;n&lt;t.length;n++){var r=t[n];r.enumerable=r.enumerable||!1,r.configurable=!0,"value"in r&amp;&amp;(r.writable=!0),Object.defineProperty(e,r.key,r)}}var u="_dashprivate_historychange",d=function(){function e(){!function(e,t){if(!(e instanceof t))throw new TypeError("Cannot call a class as a function")}(this,e)}var t,n;return t=e,n=[{key:"dispatchChangeEvent",value:function(){window.dispatchEvent(new CustomEvent(u))}},{key:"onChange",value:function(e){return window.addEventListener(u,e),function(){return window.removeEventListener(u,e)}}}],null&amp;&amp;c(t.prototype,null),n&amp;&amp;c(t,n),Object.defineProperty(t,"prototype",{writable:!1}),e}()}]))},94148:function(e,t,n){"use strict";var r=n(65606),a=n(96763);function o(e){return o="function"==typeof Symbol&amp;&amp;"symbol"==typeof Symbol.iterator?function(e){return typeof e}:function(e){return e&amp;&amp;"function"==typeof Symbol&amp;&amp;e.constructor===Symbol&amp;&amp;e!==Symbol.prototype?"symbol":typeof e},o(e)}function i(e,t){for(var n=0;n&lt;t.length;n++){var r=t[n];r.enumerable=r.enumerable||!1,r.configurable=!0,"value"in r&amp;&amp;(r.writable=!0),Object.defineProperty(e,(void 0,a=function(e,t){if("object"!==o(e)||null===e)return e;var n=e[Symbol.toPrimitive];if(void 0!==n){var r=n.call(e,"string");if("object"!==o(r))return r;throw new TypeError("@@toPrimitive must return a primitive value.")}return String(e)}(r.key),"symbol"===o(a)?a:String(a)),r)}var a}function s(e,t,n){return t&amp;&amp;i(e.prototype,t),n&amp;&amp;i(e,n),Object.defineProperty(e,"prototype",{writable:!1}),e}var l,c,u=n(69597).codes,d=u.ERR_AMBIGUOUS_ARGUMENT,g=u.ERR_INVALID_ARG_TYPE,m=u.ERR_INVALID_ARG_VALUE,_=u.ERR_INVALID_RETURN_VALUE,f=u.ERR_MISSING_ARGS,p=n(3918),A=n(40537).inspect,h=n(40537).types,y=h.isPromise,b=h.isRegExp,C=n(11514)(),I=n(9394)(),v=n(38075)("RegExp.prototype.test");function M(){var e=n(82299);l=e.isDeepEqual,c=e.isDeepStrictEqual}new Map;var k=!1,Y=e.exports=D,w={};function L(e){if(e.message instanceof Error)throw e.message;throw new p(e)}function x(e,t,n,r){if(!n){var a=!1;if(0===t)a=!0,r="No value argument passed to `assert.ok()`";else if(r instanceof Error)throw r;var o=new p({actual:n,expected:!0,message:r,operator:"==",stackStartFn:e});throw o.generatedMessage=a,o}}function D(){for(var e=arguments.length,t=new Array(e),n=0;n&lt;e;n++)t[n]=arguments[n];x.apply(void 0,[D,t.length].concat(t))}Y.fail=function e(t,n,o,i,s){var l,c=arguments.length;if(0===c?l="Failed":1===c?(o=t,t=void 0):(!1===k&amp;&amp;(k=!0,(r.emitWarning?r.emitWarning:a.warn.bind(a))("assert.fail() with more than one argument is deprecated. Please use assert.strictEqual() instead or only pass a message.","DeprecationWarning","DEP0094")),2===c&amp;&amp;(i="!=")),o instanceof Error)throw o;var u={actual:t,expected:n,operator:void 0===i?"fail":i,stackStartFn:s||e};void 0!==o&amp;&amp;(u.message=o);var d=new p(u);throw l&amp;&amp;(d.message=l,d.generatedMessage=!0),d},Y.AssertionError=p,Y.ok=D,Y.equal=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");t!=n&amp;&amp;L({actual:t,expected:n,message:r,operator:"==",stackStartFn:e})},Y.notEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");t==n&amp;&amp;L({actual:t,expected:n,message:r,operator:"!=",stackStartFn:e})},Y.deepEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");void 0===l&amp;&amp;M(),l(t,n)||L({actual:t,expected:n,message:r,operator:"deepEqual",stackStartFn:e})},Y.notDeepEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");void 0===l&amp;&amp;M(),l(t,n)&amp;&amp;L({actual:t,expected:n,message:r,operator:"notDeepEqual",stackStartFn:e})},Y.deepStrictEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");void 0===l&amp;&amp;M(),c(t,n)||L({actual:t,expected:n,message:r,operator:"deepStrictEqual",stackStartFn:e})},Y.notDeepStrictEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");void 0===l&amp;&amp;M(),c(t,n)&amp;&amp;L({actual:t,expected:n,message:r,operator:"notDeepStrictEqual",stackStartFn:e})},Y.strictEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");I(t,n)||L({actual:t,expected:n,message:r,operator:"strictEqual",stackStartFn:e})},Y.notStrictEqual=function e(t,n,r){if(arguments.length&lt;2)throw new f("actual","expected");I(t,n)&amp;&amp;L({actual:t,expected:n,message:r,operator:"notStrictEqual",stackStartFn:e})};var S=s((function e(t,n,r){var a=this;!function(e,t){if(!(e instanceof t))throw new TypeError("Cannot call a class as a function")}(this,e),n.forEach((function(e){e in t&amp;&amp;(void 0!==r&amp;&amp;"string"==typeof r[e]&amp;&amp;b(t[e])&amp;&amp;v(t[e],r[e])?a[e]=r[e]:a[e]=t[e])}))}));function B(e,t,n,r){if("function"!=typeof t){if(b(t))return v(t,e);if(2===arguments.length)throw new g("expected",["Function","RegExp"],t);if("object"!==o(e)||null===e){var a=new p({actual:e,expected:t,message:n,operator:"deepStrictEqual",stackStartFn:r});throw a.operator=r.name,a}var i=Object.keys(t);if(t instanceof Error)i.push("name","message");else if(0===i.length)throw new m("error",t,"may not be an empty object");return void 0===l&amp;&amp;M(),i.forEach((function(a){"string"==typeof e[a]&amp;&amp;b(t[a])&amp;&amp;v(t[a],e[a])||function(e,t,n,r,a,o){if(!(n in e)||!c(e[n],t[n])){if(!r){var i=new S(e,a),s=new S(t,a,e),l=new p({actual:i,expected:s,operator:"deepStrictEqual",stackStartFn:o});throw l.actual=e,l.expected=t,l.operator=o.name,l}L({actual:e,expected:t,message:r,operator:o.name,stackStartFn:o})}}(e,t,a,n,i,r)})),!0}return void 0!==t.prototype&amp;&amp;e instanceof t||!Error.isPrototypeOf(t)&amp;&amp;!0===t.call({},e)}function j(e){if("function"!=typeof e)throw new g("fn","Function",e);try{e()}catch(e){return e}return w}function T(e){return y(e)||null!==e&amp;&amp;"object"===o(e)&amp;&amp;"function"==typeof e.then&amp;&amp;"function"==typeof e.catch}function G(e){return Promise.resolve().then((function(){var t;if("function"==typeof e){if(!T(t=e()))throw new _("instance of Promise","promiseFn",t)}else{if(!T(e))throw new g("promiseFn",["Function","Promise"],e);t=e}return Promise.resolve().then((function(){return t})).then((function(){return w})).catch((function(e){return e}))}))}function H(e,t,n,r){if("string"==typeof n){if(4===arguments.length)throw new g("error",["Object","Error","Function","RegExp"],n);if("object"===o(t)&amp;&amp;null!==t){if(t.message===n)throw new d("error/message",'The error message "'.concat(t.message,'" is identical to the message.'))}else if(t===n)throw new d("error/message",'The error "'.concat(t,'" is identical to the message.'));r=n,n=void 0}else if(null!=n&amp;&amp;"object"!==o(n)&amp;&amp;"function"!=typeof n)throw new g("error",["Object","Error","Function","RegExp"],n);if(t===w){var a="";n&amp;&amp;n.name&amp;&amp;(a+=" (".concat(n.name,")")),a+=r?": ".concat(r):".";var i="rejects"===e.name?"rejection":"exception";L({actual:void 0,expected:n,operator:e.name,message:"Missing expected ".concat(i).concat(a),stackStartFn:e})}if(n&amp;&amp;!B(t,n,r,e))throw t}function E(e,t,n,r){if(t!==w){if("string"==typeof n&amp;&amp;(r=n,n=void 0),!n||B(t,n)){var a=r?": ".concat(r):".",o="doesNotReject"===e.name?"rejection":"exception";L({actual:t,expected:n,operator:e.name,message:"Got unwanted ".concat(o).concat(a,"\n")+'Actual message: "'.concat(t&amp;&amp;t.message,'"'),stackStartFn:e})}throw t}}function O(e,t,n,r,a){if(!b(t))throw new g("regexp","RegExp",t);var i="match"===a;if("string"!=typeof e||v(t,e)!==i){if(n instanceof Error)throw n;var s=!n;n=n||("string"!=typeof e?'The "string" argument must be of type string. Received type '+"".concat(o(e)," (").concat(A(e),")"):(i?"The input did not match the regular expression ":"The input was expected to not match the regular expression ")+"".concat(A(t),". Input:\n\n").concat(A(e),"\n"));var l=new p({actual:e,expected:t,message:n,operator:a,stackStartFn:r});throw l.generatedMessage=s,l}}function W(){for(var e=arguments.length,t=new Array(e),n=0;n&lt;e;n++)t[n]=arguments[n];x.apply(void 0,[W,t.length].concat(t))}Y.throws=function e(t){for(var n=arguments.length,r=new Array(n&gt;1?n-1:0),a=1;a&lt;n;a++)r[a-1]=arguments[a];H.apply(void 0,[e,j(t)].concat(r))},Y.rejects=function e(t){for(var n=arguments.length,r=new Array(n&gt;1?n-1:0),a=1;a&lt;n;a++)r[a-1]=arguments[a];return G(t).then((function(t){return H.apply(void 0,[e,t].concat(r))}))},Y.doesNotThrow=function e(t){for(var n=arguments.length,r=new Array(n&gt;1?n-1:0),a=1;a&lt;n;a++)r[a-1]=arguments[a];E.apply(void 0,[e,j(t)].concat(r))},Y.doesNotReject=function e(t){for(var n=arguments.length,r=new Array(n&gt;1?n-1:0),a=1;a&lt;n;a++)r[a-1]=arguments[a];return G(t).then((function(t){return E.apply(void 0,[e,t].concat(r))}))},Y.ifError=function e(t){if(null!=t){var n="ifError got unwanted exception: ";"object"===o(t)&amp;&amp;"string"==typeof t.message?0===t.message.length&amp;&amp;t.constructor?n+=t.constructor.name:n+=t.message:n+=A(t);var r=new p({actual:t,expected:null,operator:"ifError",message:n,stackStartFn:e}),a=t.stack;if("string"==typeof a){var i=a.split("\n");i.shift();for(var s=r.stack.split("\n"),l=0;l&lt;i.length;l++){var c=s.indexOf(i[l]);if(-1!==c){s=s.slice(0,c);break}}r.stack="".concat(s.join("\n"),"\n").concat(i.join("\n"))}throw r}},Y.match=function e(t,n,r){O(t,n,r,e,"match")},Y.doesNotMatch=function e(t,n,r){O(t,n,r,e,"doesNotMatch")},Y.strict=C(W,Y,{equal:Y.strictEqual,deepEqual:Y.deepStrictEqual,notEqual:Y.notStrictEqual,notDeepEqual:Y.notDeepStrictEqual}),Y.strict.strict=Y.strict},3918:function(e,t,n){"use strict";var r=n(65606);function a(e,t){var n=Object.keys(e);if(Object.getOwnPropertySymbols){var r=Object.getOwnPropertySymbols(e);t&amp;&amp;(r=r.filter((function(t){return Object.getOwnPropertyDescriptor(e,t).enumerable}))),n.push.apply(n,r)}return n}function o(e){for(var t=1;t&lt;arguments.length;t++){var n=null!=arguments[t]?arguments[t]:{};t%2?a(Object(n),!0).forEach((function(t){var r,a,o;r=e,a=t,o=n[t],(a=s(a))in r?Object.defineProperty(r,a,{value:o,enumerable:!0,configurable:!0,writable:!0}):r[a]=o})):Object.getOwnPropertyDescriptors?Object.defineProperties(e,Object.getOwnPropertyDescriptors(n)):a(Object(n)).forEach((function(t){Object.defineProperty(e,t,Object.getOwnPropertyDescriptor(n,t))}))}return e}function i(e,t){for(var n=0;n&lt;t.length;n++){var r=t[n];r.enumerable=r.enumerable||!1,r.configurable=!0,"value"in r&amp;&amp;(r.writable=!0),Object.defineProperty(e,s(r.key),r)}}function s(e){var t=function(e,t){if("object"!==f(e)||null===e)return e;var n=e[Symbol.toPrimitive];if(void 0!==n){var r=n.call(e,"string");if("object"!==f(r))return r;throw new TypeError("@@toPrimitive must return a primitive value.")}return String(e)}(e);return"symbol"===f(t)?t:String(t)}function l(e,t){if(t&amp;&amp;("object"===f(t)||"function"==typeof t))return t;if(void 0!==t)throw new TypeError("Derived constructors may only return object or undefined");return c(e)}function c(e){if(void 0===e)throw new ReferenceError("this hasn't been initialised - super() hasn't been called");return e}function u(e){var t="function"==typeof Map?new Map:void 0;return u=function(e){if(null===e||(n=e,-1===Function.toString.call(n).indexOf("[native code]")))return e;var n;if("function"!=typeof e)throw new TypeError("Super expression must either be null or a function");if(void 0!==t){if(t.has(e))return t.get(e);t.set(e,r)}function r(){return d(e,arguments,_(this).constructor)}return r.prototype=Object.create(e.prototype,{constructor:{value:r,enumerable:!1,writable:!0,configurable:!0}}),m(r,e)},u(e)}function d(e,t,n){return d=g()?Reflect.construct.bind():function(e,t,n){var r=[null];r.push.apply(r,t);var a=new(Function.bind.apply(e,r));return n&amp;&amp;m(a,n.prototype),a},d.apply(null,arguments)}function g(){if("undefined"==typeof Reflect||!Reflect.construct)return!1;if(Reflect.construct.sham)return!1;if("function"==typeof Proxy)return!0;try{return Boolean.prototype.valueOf.call(Reflect.construct(Boolean,[],(function(){}))),!0}catch(e){return!1}}function m(e,t){return m=Object.setPrototypeOf?Object.setPrototypeOf.bind():function(e,t){return e.__proto__=t,e},m(e,t)}function _(e){return _=Object.setPrototypeOf?Object.getPrototypeOf.bind():function(e){return e.__proto__||Object.getPrototypeOf(e)},_(e)}function f(e){return f="function"==typeof Symbol&amp;&amp;"symbol"==typeof Symbol.iterator?function(e){return typeof e}:function(e){return e&amp;&amp;"function"==typeof Symbol&amp;&amp;e.constructor===Symbol&amp;&amp;e!==Symbol.prototype?"symbol":typeof e},f(e)}var p=n(40537).inspect,A=n(69597).codes.ERR_INVALID_ARG_TYPE;function h(e,t,n){return(void 0===n||n&gt;e.length)&amp;&amp;(n=e.length),e.substring(n-t.length,n)===t}var y="",b="",C="",I="",v={deepStrictEqual:"Expected values to be strictly deep-equal:",strictEqual:"Expected values to be strictly equal:",strictEqualObject:'Expected "actual" to be reference-equal to "expected":',deepEqual:"Expected values to be loosely deep-equal:",equal:"Expected values to be loosely equal:",notDeepStrictEqual:'Expected "actual" not to be strictly deep-equal to:',notStrictEqual:'Expected "actual" to be strictly unequal to:',notStrictEqualObject:'Expected "actual" not to be reference-equal to "expected":',notDeepEqual:'Expected "actual" not to be loosely deep-equal to:',notEqual:'Expected "actual" to be loosely unequal to:',notIdentical:"Values identical but not reference-equal:"};function M(e){var t=Object.keys(e),n=Object.create(Object.getPrototypeOf(e));return t.forEach((function(t){n[t]=e[t]})),Object.defineProperty(n,"message",{value:e.message}),n}function k(e){return p(e,{compact:!1,customInspect:!1,depth:1e3,maxArrayLength:1/0,showHidden:!1,breakLength:1/0,showProxy:!1,sorted:!0,getters:!0})}var Y=function(e,t){!function(e,t){if("function"!=typeof t&amp;&amp;null!==t)throw new TypeError("Super expression must either be null or a function");e.prototype=Object.create(t&amp;&amp;t.prototype,{constructor:{value:e,writable:!0,configurable:!0}}),Object.defineProperty(e,"prototype",{writable:!1}),t&amp;&amp;m(e,t)}(Y,e);var n,a,s,u,d=(n=Y,a=g(),function(){var e,t=_(n);if(a){var r=_(this).constructor;e=Reflect.construct(t,arguments,r)}else e=t.apply(this,arguments);return l(this,e)});function Y(e){var t;if(function(e,t){if(!(e instanceof t))throw new TypeError("Cannot call a class as a function")}(this,Y),"object"!==f(e)||null===e)throw new A("options","Object",e);var n=e.message,a=e.operator,o=e.stackStartFn,i=e.actual,s=e.expected,u=Error.stackTraceLimit;if(Error.stackTraceLimit=0,null!=n)t=d.call(this,String(n));else if(r.stderr&amp;&amp;r.stderr.isTTY&amp;&amp;(r.stderr&amp;&amp;r.stderr.getColorDepth&amp;&amp;1!==r.stderr.getColorDepth()?(y="_x001B_[34m",b="_x001B_[32m",I="_x001B_[39m",C="_x001B_[31m"):(y="",b="",I="",C="")),"object"===f(i)&amp;&amp;null!==i&amp;&amp;"object"===f(s)&amp;&amp;null!==s&amp;&amp;"stack"in i&amp;&amp;i instanceof Error&amp;&amp;"stack"in s&amp;&amp;s instanceof Error&amp;&amp;(i=M(i),s=M(s)),"deepStrictEqual"===a||"strictEqual"===a)t=d.call(this,function(e,t,n){var a="",o="",i=0,s="",l=!1,c=k(e),u=c.split("\n"),d=k(t).split("\n"),g=0,m="";if("strictEqual"===n&amp;&amp;"object"===f(e)&amp;&amp;"object"===f(t)&amp;&amp;null!==e&amp;&amp;null!==t&amp;&amp;(n="strictEqualObject"),1===u.length&amp;&amp;1===d.length&amp;&amp;u[0]!==d[0]){var _=u[0].length+d[0].length;if(_&lt;=10){if(!("object"===f(e)&amp;&amp;null!==e||"object"===f(t)&amp;&amp;null!==t||0===e&amp;&amp;0===t))return"".concat(v[n],"\n\n")+"".concat(u[0]," !== ").concat(d[0],"\n")}else if("strictEqualObject"!==n&amp;&amp;_&lt;(r.stderr&amp;&amp;r.stderr.isTTY?r.stderr.columns:80)){for(;u[0][g]===d[0][g];)g++;g&gt;2&amp;&amp;(m="\n  ".concat(function(e,t){if(t=Math.floor(t),0==e.length||0==t)return"";var n=e.length*t;for(t=Math.floor(Math.log(t)/Math.log(2));t;)e+=e,t--;return e+e.substring(0,n-e.length)}(" ",g),"^"),g=0)}}for(var p=u[u.length-1],A=d[d.length-1];p===A&amp;&amp;(g++&lt;2?s="\n  ".concat(p).concat(s):a=p,u.pop(),d.pop(),0!==u.length&amp;&amp;0!==d.length);)p=u[u.length-1],A=d[d.length-1];var M=Math.max(u.length,d.length);if(0===M){var Y=c.split("\n");if(Y.length&gt;30)for(Y[26]="".concat(y,"...").concat(I);Y.length&gt;27;)Y.pop();return"".concat(v.notIdentical,"\n\n").concat(Y.join("\n"),"\n")}g&gt;3&amp;&amp;(s="\n".concat(y,"...").concat(I).concat(s),l=!0),""!==a&amp;&amp;(s="\n  ".concat(a).concat(s),a="");var w=0,L=v[n]+"\n".concat(b,"+ actual").concat(I," ").concat(C,"- expected").concat(I),x=" ".concat(y,"...").concat(I," Lines skipped");for(g=0;g&lt;M;g++){var D=g-i;if(u.length&lt;g+1)D&gt;1&amp;&amp;g&gt;2&amp;&amp;(D&gt;4?(o+="\n".concat(y,"...").concat(I),l=!0):D&gt;3&amp;&amp;(o+="\n  ".concat(d[g-2]),w++),o+="\n  ".concat(d[g-1]),w++),i=g,a+="\n".concat(C,"-").concat(I," ").concat(d[g]),w++;else if(d.length&lt;g+1)D&gt;1&amp;&amp;g&gt;2&amp;&amp;(D&gt;4?(o+="\n".concat(y,"...").concat(I),l=!0):D&gt;3&amp;&amp;(o+="\n  ".concat(u[g-2]),w++),o+="\n  ".concat(u[g-1]),w++),i=g,o+="\n".concat(b,"+").concat(I," ").concat(u[g]),w++;else{var S=d[g],B=u[g],j=B!==S&amp;&amp;(!h(B,",")||B.slice(0,-1)!==S);j&amp;&amp;h(S,",")&amp;&amp;S.slice(0,-1)===B&amp;&amp;(j=!1,B+=","),j?(D&gt;1&amp;&amp;g&gt;2&amp;&amp;(D&gt;4?(o+="\n".concat(y,"...").concat(I),l=!0):D&gt;3&amp;&amp;(o+="\n  ".concat(u[g-2]),w++),o+="\n  ".concat(u[g-1]),w++),i=g,o+="\n".concat(b,"+").concat(I," ").concat(B),a+="\n".concat(C,"-").concat(I," ").concat(S),w+=2):(o+=a,a="",1!==D&amp;&amp;0!==g||(o+="\n  ".concat(B),w++))}if(w&gt;20&amp;&amp;g&lt;M-2)return"".concat(L).concat(x,"\n").concat(o,"\n").concat(y,"...").concat(I).concat(a,"\n")+"".concat(y,"...").concat(I)}return"".concat(L).concat(l?x:"","\n").concat(o).concat(a).concat(s).concat(m)}(i,s,a));else if("notDeepStrictEqual"===a||"notStrictEqual"===a){var g=v[a],m=k(i).split("\n");if("notStrictEqual"===a&amp;&amp;"object"===f(i)&amp;&amp;null!==i&amp;&amp;(g=v.notStrictEqualObject),m.length&gt;30)for(m[26]="".concat(y,"...").concat(I);m.length&gt;27;)m.pop();t=1===m.length?d.call(this,"".concat(g," ").concat(m[0])):d.call(this,"".concat(g,"\n\n").concat(m.join("\n"),"\n"))}else{var _=k(i),p="",w=v[a];"notDeepEqual"===a||"notEqual"===a?(_="".concat(v[a],"\n\n").concat(_)).length&gt;1024&amp;&amp;(_="".concat(_.slice(0,1021),"...")):(p="".concat(k(s)),_.length&gt;512&amp;&amp;(_="".concat(_.slice(0,509),"...")),p.length&gt;512&amp;&amp;(p="".concat(p.slice(0,509),"...")),"deepEqual"===a||"equal"===a?_="".concat(w,"\n\n").concat(_,"\n\nshould equal\n\n"):p=" ".concat(a," ").concat(p)),t=d.call(this,"".concat(_).concat(p))}return Error.stackTraceLimit=u,t.generatedMessage=!n,Object.defineProperty(c(t),"name",{value:"AssertionError [ERR_ASSERTION]",enumerable:!1,writable:!0,configurable:!0}),t.code="ERR_ASSERTION",t.actual=i,t.expected=s,t.operator=a,Error.captureStackTrace&amp;&amp;Error.captureStackTrace(c(t),o),t.stack,t.name="AssertionError",l(t)}return s=Y,(u=[{key:"toString",value:function(){return"".concat(this.name," [").concat(this.code,"]: ").concat(this.message)}},{key:t,value:function(e,t){return p(this,o(o({},t),{},{customInspect:!1,depth:0}))}}])&amp;&amp;i(s.prototype,u),Object.defineProperty(s,"prototype",{writable:!1}),Y}(u(Error),p.custom);e.exports=Y},69597:function(e,t,n){"use strict";function r(e){return r="function"==typeof Symbol&amp;&amp;"symbol"==typeof Symbol.iterator?function(e){return typeof e}:function(e){return e&amp;&amp;"function"==typeof Symbol&amp;&amp;e.constructor===Symbol&amp;&amp;e!==Symbol.prototype?"symbol":typeof e},r(e)}function a(e,t){return a=Object.setPrototypeOf?Object.setPrototypeOf.bind():function(e,t){return e.__proto__=t,e},a(e,t)}function o(e){return o=Object.setPrototypeOf?Object.getPrototypeOf.bind():function(e){return e.__proto__||Object.getPrototypeOf(e)},o(e)}var i,s,l={};function c(e,t,n){n||(n=Error);var i=function(n){!function(e,t){if("function"!=typeof t&amp;&amp;null!==t)throw new TypeError("Super expression must either be null or a function");e.prototype=Object.create(t&amp;&amp;t.prototype,{constructor:{value:e,writable:!0,configurable:!0}}),Object.defineProperty(e,"prototype",{writable:!1}),t&amp;&amp;a(e,t)}(u,n);var i,s,l,c=(s=u,l=function(){if("undefined"==typeof Reflect||!Reflect.construct)return!1;if(Reflect.construct.sham)return!1;if("function"==typeof Proxy)return!0;try{return Boolean.prototype.valueOf.call(Reflect.construct(Boolean,[],(function(){}))),!0}catch(e){return!1}}(),function(){var e,t=o(s);if(l){var n=o(this).constructor;e=Reflect.construct(t,arguments,n)}else e=t.apply(this,arguments);return function(e,t){if(t&amp;&amp;("object"===r(t)||"function"==typeof t))return t;if(void 0!==t)throw new TypeError("Derived constructors may only return object or undefined");return function(e){if(void 0===e)throw new ReferenceError("this hasn't been initialised - super() hasn't been called");return e}(e)}(this,e)});function u(n,r,a){var o;return function(e,t){if(!(e instanceof t))throw new TypeError("Cannot call a class as a function")}(this,u),o=c.call(this,function(e,n,r){return"string"==typeof t?t:t(e,n,r)}(n,r,a)),o.code=e,o}return i=u,Object.defineProperty(i,"prototype",{writable:!1}),i}(n);l[e]=i}function u(e,t){if(Array.isArray(e)){var n=e.length;return e=e.map((function(e){return String(e)})),n&gt;2?"one of ".concat(t," ").concat(e.slice(0,n-1).join(", "),", or ")+e[n-1]:2===n?"one of ".concat(t," ").concat(e[0]," or ").concat(e[1]):"of ".concat(t," ").concat(e[0])}return"of ".concat(t," ").concat(String(e))}c("ERR_AMBIGUOUS_ARGUMENT",'The "%s" argument is ambiguous. %s',TypeError),c("ERR_INVALID_ARG_TYPE",(function(e,t,a){var o,s,l,c,d;if(void 0===i&amp;&amp;(i=n(94148)),i("string"==typeof e,"'name' must be a string"),"string"==typeof t&amp;&amp;(s="not ",t.substr(0,4)===s)?(o="must not be",t=t.replace(/^not /,"")):o="must be",function(e,t,n){return(void 0===n||n&gt;e.length)&amp;&amp;(n=e.length),e.substring(n-9,n)===t}(e," argument"))l="The ".concat(e," ").concat(o," ").concat(u(t,"type"));else{var g=("number"!=typeof d&amp;&amp;(d=0),d+1&gt;(c=e).length||-1===c.indexOf(".",d)?"argument":"property");l='The "'.concat(e,'" ').concat(g," ").concat(o," ").concat(u(t,"type"))}return l+". Received type ".concat(r(a))}),TypeError),c("ERR_INVALID_ARG_VALUE",(function(e,t){var r=arguments.length&gt;2&amp;&amp;void 0!==arguments[2]?arguments[2]:"is invalid";void 0===s&amp;&amp;(s=n(40537));var a=s.inspect(t);return a.length&gt;128&amp;&amp;(a="".concat(a.slice(0,128),"...")),"The argument '".concat(e,"' ").concat(r,". Received ").concat(a)}),TypeError,RangeError),c("ERR_INVALID_RETURN_VALUE",(function(e,t,n){var a;return a=n&amp;&amp;n.constructor&amp;&amp;n.constructor.name?"instance of ".concat(n.constructor.name):"type ".concat(r(n)),"Expected ".concat(e,' to be returned from the "').concat(t,'"')+" function but got ".concat(a,".")}),TypeError),c("ERR_MISSING_ARGS",(function(){for(var e=arguments.length,t=new Array(e),r=0;r&lt;e;r++)t[r]=arguments[r];void 0===i&amp;&amp;(i=n(94148)),i(t.length&gt;0,"At least one arg needs to be specified");var a="The ",o=t.length;switch(t=t.map((function(e){return'"'.concat(e,'"')})),o){case 1:a+="".concat(t[0]," argument");break;case 2:a+="".concat(t[0]," and ").concat(t[1]," arguments");break;default:a+=t.slice(0,o-1).join(", "),a+=", and ".concat(t[o-1]," arguments")}return"".concat(a," must be specified")}),TypeError),e.exports.codes=l},82299:function(e,t,n){"use strict";function r(e,t){return function(e){if(Array.isArray(e))return e}(e)||function(e,t){var n=null==e?null:"undefined"!=typeof Symbol&amp;&amp;e[Symbol.iterator]||e["@@iterator"];if(null!=n){var r,a,o,i,s=[],l=!0,c=!1;try{if(o=(n=n.call(e)).next,0===t){if(Object(n)!==n)return;l=!1}else for(;!(l=(r=o.call(n)).done)&amp;&amp;(s.push(r.value),s.length!==t);l=!0);}catch(e){c=!0,a=e}finally{try{if(!l&amp;&amp;null!=n.return&amp;&amp;(i=n.return(),Object(i)!==i))return}finally{if(c)throw a}}return s}}(e,t)||function(e,t){if(e){if("string"==typeof e)return a(e,t);var n=Object.prototype.toString.call(e).slice(8,-1);return"Object"===n&amp;&amp;e.constructor&amp;&amp;(n=e.constructor.name),"Map"===n||"Set"===n?Array.from(e):"Arguments"===n||/^(?:Ui|I)nt(?:8|16|32)(?:Clamped)?Array$/.test(n)?a(e,t):void 0}}(e,t)||function(){throw new TypeError("Invalid attempt to destructure non-iterable instance.\nIn order to be iterable, non-array objects must have a [Symbol.iterator]() method.")}()}function a(e,t){(null==t||t&gt;e.length)&amp;&amp;(t=e.length);for(var n=0,r=new Array(t);n&lt;t;n++)r[n]=e[n];return r}function o(e){return o="function"==typeof Symbol&amp;&amp;"symbol"==typeof Symbol.iterator?function(e){return typeof e}:function(e){return e&amp;&amp;"function"==typeof Symbol&amp;&amp;e.constructor===Symbol&amp;&amp;e!==Symbol.prototype?"symbol":typeof e},o(e)}var i=void 0!==/a/g.flags,s=function(e){var t=[];return e.forEach((function(e){return t.push(e)})),t},l=function(e){var t=[];return e.forEach((function(e,n){return t.push([n,e])})),t},c=Object.is?Object.is:n(37653),u=Object.getOwnPropertySymbols?Object.getOwnPropertySymbols:function(){return[]},d=Number.isNaN?Number.isNaN:n(24133);function g(e){return e.call.bind(e)}var m=g(Object.prototype.hasOwnProperty),_=g(Object.prototype.propertyIsEnumerable),f=g(Object.prototype.toString),p=n(40537).types,A=p.isAnyArrayBuffer,h=p.isArrayBufferView,y=p.isDate,b=p.isMap,C=p.isRegExp,I=p.isSet,v=p.isNativeError,M=p.isBoxedPrimitive,k=p.isNumberObject,Y=p.isStringObject,w=p.isBooleanObject,L=p.isBigIntObject,x=p.isSymbolObject,D=p.isFloat32Array,S=p.isFloat64Array;function B(e){if(0===e.length||e.length&gt;10)return!0;for(var t=0;t&lt;e.length;t++){var n=e.charCodeAt(t);if(n&lt;48||n&gt;57)return!0}return 10===e.length&amp;&amp;e&gt;=Math.pow(2,32)}function j(e){return Object.keys(e).filter(B).concat(u(e).filter(Object.prototype.propertyIsEnumerable.bind(e)))}function T(e,t){if(e===t)return 0;for(var n=e.length,r=t.length,a=0,o=Math.min(n,r);a&lt;o;++a)if(e[a]!==t[a]){n=e[a],r=t[a];break}return n&lt;r?-1:r&lt;n?1:0}var G=0,H=1,E=2,O=3;function W(e,t,n,r){if(e===t)return 0!==e||!n||c(e,t);if(n){if("object"!==o(e))return"number"==typeof e&amp;&amp;d(e)&amp;&amp;d(t);if("object"!==o(t)||null===e||null===t)return!1;if(Object.getPrototypeOf(e)!==Object.getPrototypeOf(t))return!1}else{if(null===e||"object"!==o(e))return(null===t||"object"!==o(t))&amp;&amp;e==t;if(null===t||"object"!==o(t))return!1}var a,s,l,u,g=f(e);if(g!==f(t))return!1;if(Array.isArray(e)){if(e.length!==t.length)return!1;var m=j(e),_=j(t);return m.length===_.length&amp;&amp;F(e,t,n,r,H,m)}if("[object Object]"===g&amp;&amp;(!b(e)&amp;&amp;b(t)||!I(e)&amp;&amp;I(t)))return!1;if(y(e)){if(!y(t)||Date.prototype.getTime.call(e)!==Date.prototype.getTime.call(t))return!1}else if(C(e)){if(!C(t)||(l=e,u=t,!(i?l.source===u.source&amp;&amp;l.flags===u.flags:RegExp.prototype.toString.call(l)===RegExp.prototype.toString.call(u))))return!1}else if(v(e)||e instanceof Error){if(e.message!==t.message||e.name!==t.name)return!1}else{if(h(e)){if(n||!D(e)&amp;&amp;!S(e)){if(!function(e,t){return e.byteLength===t.byteLength&amp;&amp;0===T(new Uint8Array(e.buffer,e.byteOffset,e.byteLength),new Uint8Array(t.buffer,t.byteOffset,t.byteLength))}(e,t))return!1}else if(!function(e,t){if(e.byteLength!==t.byteLength)return!1;for(var n=0;n&lt;e.byteLength;n++)if(e[n]!==t[n])return!1;return!0}(e,t))return!1;var p=j(e),B=j(t);return p.length===B.length&amp;&amp;F(e,t,n,r,G,p)}if(I(e))return!(!I(t)||e.size!==t.size)&amp;&amp;F(e,t,n,r,E);if(b(e))return!(!b(t)||e.size!==t.size)&amp;&amp;F(e,t,n,r,O);if(A(e)){if(s=t,(a=e).byteLength!==s.byteLength||0!==T(new Uint8Array(a),new Uint8Array(s)))return!1}else if(M(e)&amp;&amp;!function(e,t){return k(e)?k(t)&amp;&amp;c(Number.prototype.valueOf.call(e),Number.prototype.valueOf.call(t)):Y(e)?Y(t)&amp;&amp;String.prototype.valueOf.call(e)===String.prototype.valueOf.call(t):w(e)?w(t)&amp;&amp;Boolean.prototype.valueOf.call(e)===Boolean.prototype.valueOf.call(t):L(e)?L(t)&amp;&amp;BigInt.prototype.valueOf.call(e)===BigInt.prototype.valueOf.call(t):x(t)&amp;&amp;Symbol.prototype.valueOf.call(e)===Symbol.prototype.valueOf.call(t)}(e,t))return!1}return F(e,t,n,r,G)}function P(e,t){return t.filter((function(t){return _(e,t)}))}function F(e,t,n,a,i,c){if(5===arguments.length){c=Object.keys(e);var d=Object.keys(t);if(c.length!==d.length)return!1}for(var g=0;g&lt;c.length;g++)if(!m(t,c[g]))return!1;if(n&amp;&amp;5===arguments.length){var f=u(e);if(0!==f.length){var p=0;for(g=0;g&lt;f.length;g++){var A=f[g];if(_(e,A)){if(!_(t,A))return!1;c.push(A),p++}else if(_(t,A))return!1}var h=u(t);if(f.length!==h.length&amp;&amp;P(t,h).length!==p)return!1}else{var y=u(t);if(0!==y.length&amp;&amp;0!==P(t,y).length)return!1}}if(0===c.length&amp;&amp;(i===G||i===H&amp;&amp;0===e.length||0===e.size))return!0;if(void 0===a)a={val1:new Map,val2:new Map,position:0};else{var b=a.val1.get(e);if(void 0!==b){var C=a.val2.get(t);if(void 0!==C)return b===C}a.position++}a.val1.set(e,a.position),a.val2.set(t,a.position);var I=function(e,t,n,a,i,c){var u=0;if(c===E){if(!function(e,t,n,r){for(var a=null,i=s(e),l=0;l&lt;i.length;l++){var c=i[l];if("object"===o(c)&amp;&amp;null!==c)null===a&amp;&amp;(a=new Set),a.add(c);else if(!t.has(c)){if(n)return!1;if(!N(e,t,c))return!1;null===a&amp;&amp;(a=new Set),a.add(c)}}if(null!==a){for(var u=s(t),d=0;d&lt;u.length;d++){var g=u[d];if("object"===o(g)&amp;&amp;null!==g){if(!Z(a,g,n,r))return!1}else if(!n&amp;&amp;!e.has(g)&amp;&amp;!Z(a,g,n,r))return!1}return 0===a.size}return!0}(e,t,n,i))return!1}else if(c===O){if(!function(e,t,n,a){for(var i=null,s=l(e),c=0;c&lt;s.length;c++){var u=r(s[c],2),d=u[0],g=u[1];if("object"===o(d)&amp;&amp;null!==d)null===i&amp;&amp;(i=new Set),i.add(d);else{var m=t.get(d);if(void 0===m&amp;&amp;!t.has(d)||!W(g,m,n,a)){if(n)return!1;if(!X(e,t,d,g,a))return!1;null===i&amp;&amp;(i=new Set),i.add(d)}}}if(null!==i){for(var _=l(t),f=0;f&lt;_.length;f++){var p=r(_[f],2),A=p[0],h=p[1];if("object"===o(A)&amp;&amp;null!==A){if(!z(i,e,A,h,n,a))return!1}else if(!(n||e.has(A)&amp;&amp;W(e.get(A),h,!1,a)||z(i,e,A,h,!1,a)))return!1}return 0===i.size}return!0}(e,t,n,i))return!1}else if(c===H)for(;u&lt;e.length;u++){if(!m(e,u)){if(m(t,u))return!1;for(var d=Object.keys(e);u&lt;d.length;u++){var g=d[u];if(!m(t,g)||!W(e[g],t[g],n,i))return!1}return d.length===Object.keys(t).length}if(!m(t,u)||!W(e[u],t[u],n,i))return!1}for(u=0;u&lt;a.length;u++){var _=a[u];if(!W(e[_],t[_],n,i))return!1}return!0}(e,t,n,c,a,i);return a.val1.delete(e),a.val2.delete(t),I}function Z(e,t,n,r){for(var a=s(e),o=0;o&lt;a.length;o++){var i=a[o];if(W(t,i,n,r))return e.delete(i),!0}return!1}function R(e){switch(o(e)){case"undefined":return null;case"object":return;case"symbol":return!1;case"string":e=+e;case"number":if(d(e))return!1}return!0}function N(e,t,n){var r=R(n);return null!=r?r:t.has(r)&amp;&amp;!e.has(r)}function X(e,t,n,r,a){var o=R(n);if(null!=o)return o;var i=t.get(o);return!(void 0===i&amp;&amp;!t.has(o)||!W(r,i,!1,a))&amp;&amp;!e.has(o)&amp;&amp;W(r,i,!1,a)}function z(e,t,n,r,a,o){for(var i=s(e),l=0;l&lt;i.length;l++){var c=i[l];if(W(n,c,a,o)&amp;&amp;W(r,t.get(c),a,o))return e.delete(c),!0}return!1}e.exports={isDeepEqual:function(e,t){return W(e,t,!1)},isDeepStrictEqual:function(e,t){return W(e,t,!0)}}},41334:function(e,t,n){"use strict";n.d(t,{Ay:function(){return p},Gs:function(){return h},tu:function(){return A}});var r=n(76120),a=n.n(r),o=n(51609),i=n.n(o),s=function(){return Promise.all([n.e(384),n.e(400)]).then(n.bind(n,69945))},l=n(2654);function c(e,t){for(var n=0;n&lt;t.length;n++){var r=t[n];r.enumerable=r.enumerable||!1,r.configurable=!0,"value"in r&amp;&amp;(r.writable=!0),Object.defineProperty(e,u(r.key),r)}}function u(e){var t=function(e,t){if("object"!=typeof e||!e)return e;var n=e[Symbol.toPrimitive];if(void 0!==n){var r=n.call(e,"string");if("object"!=typeof r)return r;throw new TypeError("@@toPrimitive must return a primitive value.")}return String(e)}(e);return"symbol"==typeof t?t:t+""}function d(e,t,n){return t=m(t),function(e,t){if(t&amp;&amp;("object"==typeof t||"function"==typeof t))return t;if(void 0!==t)throw new TypeError("Derived constructors may only return object or undefined");re</t>
+  </si>
+  <si>
+    <t>033 248 248</t>
+  </si>
+  <si>
+    <t>react-dates@20.1.0-fix.css</t>
+  </si>
+  <si>
+    <t>http://momentjs.com/guides/#/warnings/define-locale/</t>
+  </si>
+  <si>
+    <t>u05FF</t>
+  </si>
+  <si>
+    <t>C:\AAYS_GITHUB_BRIDGE_CLEAN2\ai-data\ty150-nista-pipeline-deep-discovery\raw\https___unpkg.com_dash-core-components_2.14.3_dash_core_components_dash_core_components.js.txt</t>
+  </si>
+  <si>
+    <t>EA-REVIEW-EA-CAND-000028</t>
+  </si>
+  <si>
+    <t>EA-CAND-000028</t>
+  </si>
+  <si>
+    <t>!function(e,n){"object"==typeof exports&amp;&amp;"object"==typeof module?module.exports=n(require("react"),require("react-dom")):"function"==typeof define&amp;&amp;define.amd?define(["react","react-dom"],n):"object"==typeof exports?exports.dash_mantine_components=n(require("react"),require("react-dom")):e.dash_mantine_components=n(e.React,e.ReactDOM)}(self,((e,n)=&gt;(()=&gt;{var t,r,a,o,i={155:(e,n,t)=&gt;{"use strict";t.d(n,{X:()=&gt;p});var r=t(3052),a=(t(295),t(4848),t(8149)),o=t(9569);function i(e,n){const t=(0,o.g)({color:e,theme:n});return"dimmed"===t.color?"var(--mantine-color-dimmed)":"bright"===t.color?"var(--mantine-color-bright)":t.variable?`var(${t.variable})`:t.color}const s={text:"var(--mantine-font-family)",mono:"var(--mantine-font-family-monospace)",monospace:"var(--mantine-font-family-monospace)",heading:"var(--mantine-font-family-headings)",headings:"var(--mantine-font-family-headings)"},l=["h1","h2","h3","h4","h5","h6"],c=["h1","h2","h3","h4","h5","h6"],d={color:i,textColor:function(e,n){const t=(0,o.g)({color:e,theme:n});return t.isThemeColor&amp;&amp;void 0===t.shade?`var(--mantine-color-${t.color}-text)`:i(e,n)},fontSize:function(e,n){return"string"==typeof e&amp;&amp;e in n.fontSizes?`var(--mantine-font-size-${e})`:"string"==typeof e&amp;&amp;l.includes(e)?`var(--mantine-${e}-font-size)`:"number"==typeof e||"string"==typeof e?(0,a.D)(e):e},spacing:function(e,n){if("number"==typeof e)return(0,a.D)(e);if("string"==typeof e){const t=e.replace("-","");if(!(t in n.spacing))return(0,a.D)(e);const r=`--mantine-spacing-${t}`;return e.startsWith("-")?`calc(var(${r}) * -1)`:`var(${r})`}return e},radius:function(e,n){return"string"==typeof e&amp;&amp;e in n.radius?`var(--mantine-radius-${e})`:"number"==typeof e||"string"==typeof e?(0,a.D)(e):e},identity:function(e){return e},size:function(e){return"number"==typeof e?(0,a.D)(e):e},lineHeight:function(e,n){return"string"==typeof e&amp;&amp;e in n.lineHeights?`var(--mantine-line-height-${e})`:"string"==typeof e&amp;&amp;c.includes(e)?`var(--mantine-${e}-line-height)`:e},fontFamily:function(e){return"string"==typeof e&amp;&amp;e in s?s[e]:e},border:function(e,n){if("number"==typeof e)return(0,a.D)(e);if("string"==typeof e){const[t,r,...o]=e.split(" ").filter((e=&gt;""!==e.trim()));let s=`${(0,a.D)(t)}`;return r&amp;&amp;(s+=` ${r}`),o.length&gt;0&amp;&amp;(s+=` ${i(o.join(" "),n)}`),s.trim()}return e}};function u(e){return e.replace("(min-width: ","").replace("em)","")}function m(e,n){return"object"==typeof e&amp;&amp;null!==e&amp;&amp;n in e?e[n]:e}function p({styleProps:e,data:n,theme:t}){return function({media:e,...n}){return{...n,media:Object.keys(e).sort(((e,n)=&gt;Number(u(e))-Number(u(n)))).map((n=&gt;({query:n,styles:e[n]})))}}((0,r.H)(e).reduce(((a,o)=&gt;{if("hiddenFrom"===o||"visibleFrom"===o||"sx"===o)return a;const i=n[o],s=Array.isArray(i.property)?i.property:[i.property],l="object"==typeof(c=e[o])&amp;&amp;null!==c?"base"in c?c.base:void 0:c;var c;if(!function(e){if("object"!=typeof e||null===e)return!1;const n=Object.keys(e);return 1!==n.length||"base"!==n[0]}(e[o]))return s.forEach((e=&gt;{a.inlineStyles[e]=d[i.type](l,t)})),a;a.hasResponsiveStyles=!0;const u=function(e){return"object"==typeof e&amp;&amp;null!==e?(0,r.H)(e).filter((e=&gt;"base"!==e)):[]}(e[o]);return s.forEach((n=&gt;{l&amp;&amp;(a.styles[n]=d[i.type](l,t)),u.forEach((r=&gt;{const s=`(min-width: ${t.breakpoints[r]})`;a.media[s]={...a.media[s],[n]:d[i.type](m(e[o],r),t)}}))})),a}),{hasResponsiveStyles:!1,styles:{},inlineStyles:{},media:{}}))}},280:(e,n,t)=&gt;{"use strict";t.d(n,{r:()=&gt;a});var r=t(8459);function a(e,n){return e in n?(0,r.px)(n[e]):(0,r.px)(e)}},295:n=&gt;{"use strict";n.exports=e},297:(e,n,t)=&gt;{"use strict";t.d(n,{C:()=&gt;a});var r=t(295);function a(e,n){const t=(0,r.useRef)(!1);(0,r.useEffect)((()=&gt;()=&gt;{t.current=!1}),[]),(0,r.useEffect)((()=&gt;{if(t.current)return e();t.current=!0}),n)}},355:(e,n,t)=&gt;{"use strict";t.d(n,{J:()=&gt;v});var r=t(4848),a=t(8149),o=t(295),i=t(6324),s=t(9396),l=t(6100),c=t(2837),d=t(8639),u=t(6076);const m=(0,o.forwardRef)((({size:e="var(--cb-icon-size, 70%)",style:n,...t},a)=&gt;(0,r.jsx)("svg",{viewBox:"0 0 15 15",fill:"none",xmlns:"http://www.w3.org/2000/svg",style:{...n,width:e,height:e},ref:a,...t,children:(0,r.jsx)("path",{d:"M11.7816 4.03157C12.0062 3.80702 12.0062 3.44295 11.7816 3.2184C11.5571 2.99385 11.193 2.99385 10.9685 3.2184L7.50005 6.68682L4.03164 3.2184C3.80708 2.99385 3.44301 2.99385 3.21846 3.2184C2.99391 3.44295 2.99391 3.80702 3.21846 4.03157L6.68688 7.49999L3.21846 10.9684C2.99391 11.193 2.99391 11.557 3.21846 11.7816C3.44301 12.0061 3.80708 12.0061 4.03164 11.7816L7.50005 8.31316L10.9685 11.7816C11.193 12.0061 11.5571 12.0061 11.7816 11.7816C12.0062 11.557 12.0062 11.193 11.7816 10.9684L8.31322 7.49999L11.7816 4.03157Z",fill:"currentColor",fillRule:"evenodd",clipRule:"evenodd"})})));m.displayName="@mantine/core/CloseIcon";var p={root:"m_86a44da5","root--subtle":"m_220c80f2"};const f={variant:"subtle"},h=(0,s.V)(((e,{size:n,radius:t,iconSize:r})=&gt;({root:{"--cb-size":(0,i.YC)(n,"cb-size"),"--cb-radius":void 0===t?void 0:(0,i.nJ)(t),"--cb-icon-size":(0,a.D)(r)}}))),v=(0,d.v)(((e,n)=&gt;{const t=(0,l.Y)("CloseButton",f,e),{iconSize:a,children:o,vars:i,radius:s,className:d,classNames:v,style:g,styles:b,unstyled:y,"data-disabled":w,disabled:_,variant:x,icon:C,mod:k,__staticSelector:S,...P}=t,N=(0,c.I)({name:S||"CloseButton",props:t,className:d,style:g,classes:p,classNames:v,styles:b,unstyled:y,vars:i,varsResolver:h});return(0,r.jsxs)(u.N,{ref:n,...P,unstyled:y,variant:x,disabled:_,mod:[{disabled:_||w},k],...N("root",{variant:x,active:!_&amp;&amp;!w}),children:[C||(0,r.jsx)(m,{}),o]})}));v.classes=p,v.displayName="@mantine/core/CloseButton"},445:function(e){e.exports=function(){"use strict";var e={LTS:"h:mm:ss A",LT:"h:mm A",L:"MM/DD/YYYY",LL:"MMMM D, YYYY",LLL:"MMMM D, YYYY h:mm A",LLLL:"dddd, MMMM D, YYYY h:mm A"},n=/(\[[^[]*\])|([-_:/.,()\s]+)|(A|a|Q|YYYY|YY?|ww?|MM?M?M?|Do|DD?|hh?|HH?|mm?|ss?|S{1,3}|z|ZZ?)/g,t=/\d/,r=/\d\d/,a=/\d\d?/,o=/\d*[^-_:/,()\s\d]+/,i={},s=function(e){return(e=+e)+(e&gt;68?1900:2e3)},l=function(e){return function(n){this[e]=+n}},c=[/[+-]\d\d:?(\d\d)?|Z/,function(e){(this.zone||(this.zone={})).offset=function(e){if(!e)return 0;if("Z"===e)return 0;var n=e.match(/([+-]|\d\d)/g),t=60*n[1]+(+n[2]||0);return 0===t?0:"+"===n[0]?-t:t}(e)}],d=function(e){var n=i[e];return n&amp;&amp;(n.indexOf?n:n.s.concat(n.f))},u=function(e,n){var t,r=i.meridiem;if(r){for(var a=1;a&lt;=24;a+=1)if(e.indexOf(r(a,0,n))&gt;-1){t=a&gt;12;break}}else t=e===(n?"pm":"PM");return t},m={A:[o,function(e){this.afternoon=u(e,!1)}],a:[o,function(e){this.afternoon=u(e,!0)}],Q:[t,function(e){this.month=3*(e-1)+1}],S:[t,function(e){this.milliseconds=100*+e}],SS:[r,function(e){this.milliseconds=10*+e}],SSS:[/\d{3}/,function(e){this.milliseconds=+e}],s:[a,l("seconds")],ss:[a,l("seconds")],m:[a,l("minutes")],mm:[a,l("minutes")],H:[a,l("hours")],h:[a,l("hours")],HH:[a,l("hours")],hh:[a,l("hours")],D:[a,l("day")],DD:[r,l("day")],Do:[o,function(e){var n=i.ordinal,t=e.match(/\d+/);if(this.day=t[0],n)for(var r=1;r&lt;=31;r+=1)n(r).replace(/\[|\]/g,"")===e&amp;&amp;(this.day=r)}],w:[a,l("week")],ww:[r,l("week")],M:[a,l("month")],MM:[r,l("month")],MMM:[o,function(e){var n=d("months"),t=(d("monthsShort")||n.map((function(e){return e.slice(0,3)}))).indexOf(e)+1;if(t&lt;1)throw new Error;this.month=t%12||t}],MMMM:[o,function(e){var n=d("months").indexOf(e)+1;if(n&lt;1)throw new Error;this.month=n%12||n}],Y:[/[+-]?\d+/,l("year")],YY:[r,function(e){this.year=s(e)}],YYYY:[/\d{4}/,l("year")],Z:c,ZZ:c};function p(t){var r,a;r=t,a=i&amp;&amp;i.formats;for(var o=(t=r.replace(/(\[[^\]]+])|(LTS?|l{1,4}|L{1,4})/g,(function(n,t,r){var o=r&amp;&amp;r.toUpperCase();return t||a[r]||e[r]||a[o].replace(/(\[[^\]]+])|(MMMM|MM|DD|dddd)/g,(function(e,n,t){return n||t.slice(1)}))}))).match(n),s=o.length,l=0;l&lt;s;l+=1){var c=o[l],d=m[c],u=d&amp;&amp;d[0],p=d&amp;&amp;d[1];o[l]=p?{regex:u,parser:p}:c.replace(/^\[|\]$/g,"")}return function(e){for(var n={},t=0,r=0;t&lt;s;t+=1){var a=o[t];if("string"==typeof a)r+=a.length;else{var i=a.regex,l=a.parser,c=e.slice(r),d=i.exec(c)[0];l.call(n,d),e=e.replace(d,"")}}return function(e){var n=e.afternoon;if(void 0!==n){var t=e.hours;n?t&lt;12&amp;&amp;(e.hours+=12):12===t&amp;&amp;(e.hours=0),delete e.afternoon}}(n),n}}return function(e,n,t){t.p.customParseFormat=!0,e&amp;&amp;e.parseTwoDigitYear&amp;&amp;(s=e.parseTwoDigitYear);var r=n.prototype,a=r.parse;r.parse=function(e){var n=e.date,r=e.utc,o=e.args;this.$u=r;var s=o[1];if("string"==typeof s){var l=!0===o[2],c=!0===o[3],d=l||c,u=o[2];c&amp;&amp;(u=o[2]),i=this.$locale(),!l&amp;&amp;u&amp;&amp;(i=t.Ls[u]),this.$d=function(e,n,t,r){try{if(["x","X"].indexOf(n)&gt;-1)return new Date(("X"===n?1e3:1)*e);var a=p(n)(e),o=a.year,i=a.month,s=a.day,l=a.hours,c=a.minutes,d=a.seconds,u=a.milliseconds,m=a.zone,f=a.week,h=new Date,v=s||(o||i?1:h.getDate()),g=o||h.getFullYear(),b=0;o&amp;&amp;!i||(b=i&gt;0?i-1:h.getMonth());var y,w=l||0,_=c||0,x=d||0,C=u||0;return m?new Date(Date.UTC(g,b,v,w,_,x,C+60*m.offset*1e3)):t?new Date(Date.UTC(g,b,v,w,_,x,C)):(y=new Date(g,b,v,w,_,x,C),f&amp;&amp;(y=r(y).week(f).toDate()),y)}catch(e){return new Date("")}}(n,s,r,t),this.init(),u&amp;&amp;!0!==u&amp;&amp;(this.$L=this.locale(u).$L),d&amp;&amp;n!=this.format(s)&amp;&amp;(this.$d=new Date("")),i={}}else if(s instanceof Array)for(var m=s.length,f=1;f&lt;=m;f+=1){o[1]=s[f-1];var h=t.apply(this,o);if(h.isValid()){this.$d=h.$d,this.$L=h.$L,this.init();break}f===m&amp;&amp;(this.$d=new Date(""))}else a.call(this,e)}}}()},540:e=&gt;{"use strict";e.exports=function(e){var n=document.createElement("style");return e.setAttributes(n,e.attributes),e.insert(n,e.options),n}},684:(e,n,t)=&gt;{"use strict";function r(e,n){return"number"==typeof e.primaryShade?e.primaryShade:"dark"===n?e.primaryShade.dark:e.primaryShade.light}t.d(n,{g:()=&gt;r})},977:(e,n,t)=&gt;{"use strict";t.d(n,{M:()=&gt;a});var r=t(295);function a(e,n,t){(0,r.useEffect)((()=&gt;(window.addEventListener(e,n,t),()=&gt;window.removeEventListener(e,n,t))),[e,n])}},1020:(e,n,t)=&gt;{"use strict";var r=t(295),a=Symbol.for("react.element"),o=Symbol.for("react.fragment"),i=Object.prototype.hasOwnProperty,s=r.__SECRET_INTERNALS_DO_NOT_USE_OR_YOU_WILL_BE_FIRED.ReactCurrentOwner,l={key:!0,ref:!0,__self:!0,__source:!0};function c(e,n,t){var r,o={},c=null,d=null;for(r in void 0!==t&amp;&amp;(c=""+t),void 0!==n.key&amp;&amp;(c=""+n.key),void 0!==n.ref&amp;&amp;(d=n.ref),n)i.call(n,r)&amp;&amp;!l.hasOwnProperty(r)&amp;&amp;(o[r]=n[r]);if(e&amp;&amp;e.defaultProps)for(r in n=e.defaultProps)void 0===o[r]&amp;&amp;(o[r]=n[r]);return{$$typeof:a,type:e,key:c,ref:d,props:o,_owner:s.current}}n.Fragment=o,n.jsx=c,n.jsxs=c},1069:(e,n,t)=&gt;{"use strict";function r(e,n){return Object.prototype.hasOwnProperty.call(n,e)}t.d(n,{A:()=&gt;r})},1101:(e,n,t)=&gt;{"use strict";t.d(n,{nW:()=&gt;f,xd:()=&gt;p});var r=t(4848),a=t(295),o=t(5304),i=t(1518);const s="[@mantine/core] MantineProvider: Invalid theme.primaryColor, it accepts only key of theme.colors, learn more – https://mantine.dev/theming/colors/#primary-color",l="[@mantine/core] MantineProvider: Invalid theme.primaryShade, it accepts only 0-9 integers or an object { light: 0-9, dark: 0-9 }";function c(e){return!(e&lt;0||e&gt;9)&amp;&amp;parseInt(e.toString(),10)===e}function d(e){if(!(e.primaryColor in e.colors))throw new Error(s);if(!("object"!=typeof e.primaryShade||c(e.primaryShade.dark)&amp;&amp;c(e.primaryShade.light)))throw new Error(l);if("number"==typeof e.primaryShade&amp;&amp;!c(e.primaryShade))throw new Error(l)}const u=(0,a.createContext)(null),m=()=&gt;(0,a.useContext)(u)||o.S;function p(){const e=(0,a.useContext)(u);if(!e)throw new Error("@mantine/core: MantineProvider was not found in component tree, make sure you have it in your app");return e}function f({theme:e,children:n,inherit:t=!0}){const s=m(),l=(0,a.useMemo)((()=&gt;function(e,n){if(!n)return d(e),e;const t=(0,i.$)(e,n);return n.fontFamily&amp;&amp;!n.headings?.fontFamily&amp;&amp;(t.headings.fontFamily=n.fontFamily),d(t),t}(t?s:o.S,e)),[e,s,t]);return(0,r.jsx)(u.Provider,{value:l,children:n})}f.displayName="@mantine/core/MantineThemeProvider"},1113:e=&gt;{"use strict";e.exports=function(e,n){if(n.styleSheet)n.styleSheet.cssText=e;else{for(;n.firstChild;)n.removeChild(n.firstChild);n.appendChild(document.createTextNode(e))}}},1228:(e,n,t)=&gt;{"use strict";function r(e,n=0,t=10**n){return Math.round(t*e)/t}t.d(n,{H0:()=&gt;h,LI:()=&gt;r,Yc:()=&gt;f});const a={grad:.9,turn:360,rad:360/(2*Math.PI)};function o(e,n="deg"){return Number(e)*(a[n]||1)}const i=/hsla?\(?\s*(-?\d*\.?\d+)(deg|rad|grad|turn)?[,\s]+(-?\d*\.?\d+)%?[,\s]+(-?\d*\.?\d+)%?,?\s*[/\s]*(-?\d*\.?\d+)?(%)?\s*\)?/i;function s(e){const n=i.exec(e);return n?function({h:e,s:n,l:t,a:r}){const a=n*((t&lt;50?t:100-t)/100);return{h:e,s:a&gt;0?2*a/(t+a)*100:0,v:t+a,a:r}}({h:o(n[1],n[2]),s:Number(n[3]),l:Number(n[4]),a:void 0===n[5]?1:Number(n[5])/(n[6]?100:1)}):{h:0,s:0,v:0,a:1}}function l({r:e,g:n,b:t,a}){const o=Math.max(e,n,t),i=o-Math.min(e,n,t),s=i?o===e?(n-t)/i:o===n?2+(t-e)/i:4+(e-n)/i:0;return{h:r(60*(s&lt;0?s+6:s),3),s:r(o?i/o*100:0,3),v:r(o/255*100,3),a}}function c(e){const n="#"===e[0]?e.slice(1):e;return 3===n.length?l({r:parseInt(n[0]+n[0],16),g:parseInt(n[1]+n[1],16),b:parseInt(n[2]+n[2],16),a:1}):l({r:parseInt(n.slice(0,2),16),g:parseInt(n.slice(2,4),16),b:parseInt(n.slice(4,6),16),a:1})}const d=/rgba?\(?\s*(-?\d*\.?\d+)(%)?[,\s]+(-?\d*\.?\d+)(%)?[,\s]+(-?\d*\.?\d+)(%)?,?\s*[/\s]*(-?\d*\.?\d+)?(%)?\s*\)?/i;function u(e){const n=d.exec(e);return n?l({r:Number(n[1])/(n[2]?100/255:1),g:Number(n[3])/(n[4]?100/255:1),b:Number(n[5])/(n[6]?100/255:1),a:void 0===n[7]?1:Number(n[7])/(n[8]?100:1)}):{h:0,s:0,v:0,a:1}}const m={hex:/^#?([0-9A-F]{3}){1,2}$/i,hexa:/^#?([0-9A-F]{4}){1,2}$/i,rgb:/^rgb\((\d+),\s*(\d+),\s*(\d+)(?:,\s*(\d+(?:\.\d+)?))?\)$/i,rgba:/^rgba\((\d+),\s*(\d+),\s*(\d+)(?:,\s*(\d+(?:\.\d+)?))?\)$/i,hsl:/hsl\(\s*(\d+)\s*,\s*(\d+(?:\.\d+)?%)\s*,\s*(\d+(?:\.\d+)?%)\)/i,hsla:/^hsla\((\d+),\s*([\d.]+)%,\s*([\d.]+)%,\s*(\d*(?:\.\d+)?)\)$/i},p={hex:c,hexa:function(e){const n="#"===e[0]?e.slice(1):e,t=e=&gt;r(parseInt(e,16)/255,3);if(4===n.length){const e=n.slice(0,3),r=t(n[3]+n[3]);return{...c(e),a:r}}const a=n.slice(0,6),o=t(n.slice(6,8));return{...c(a),a:o}},rgb:u,rgba:u,hsl:s,hsla:s};function f(e){for(const[,n]of Object.entries(m))if(n.test(e))return!0;return!1}function h(e){if("string"!=typeof e)return{h:0,s:0,v:0,a:1};if("transparent"===e)return{h:0,s:0,v:0,a:0};const n=e.trim();for(const[e,t]of Object.entries(m))if(t.test(n))return p[e](n);return{h:0,s:0,v:0,a:1}}},1322:(e,n,t)=&gt;{"use strict";t.d(n,{A:()=&gt;r});const r=(0,t(3579).A)((function(e){return null===e?"Null":void 0===e?"Undefined":Object.prototype.toString.call(e).slice(8,-1)}))},1518:(e,n,t)=&gt;{"use strict";function r(e){return e&amp;&amp;"object"==typeof e&amp;&amp;!Array.isArray(e)}function a(e,n){const t={...e},o=n;return r(e)&amp;&amp;r(n)&amp;&amp;Object.keys(n).forEach((n=&gt;{r(o[n])?t[n]=n in e?a(t[n],o[n]):o[n]:t[n]=o[n]})),t}t.d(n,{$:()=&gt;a})},1601:e=&gt;{"use strict";e.exports=function(e){return e[1]}},1617:(e,n,t)=&gt;{"use strict";t.d(n,{Z:()=&gt;a});var r=t(295);function a({value:e,defaultValue:n,finalValue:t,onChange:a=()=&gt;{}}){const[o,i]=(0,r.useState)(void 0!==n?n:t);return void 0!==e?[e,a,!0]:[o,(e,...n)=&gt;{i(e),a?.(e,...n)},!1]}},1635:(e,n,t)=&gt;{"use strict";t.d(n,{Cl:()=&gt;r,Tt:()=&gt;a,fX:()=&gt;o});var r=function(){return r=Object.assign||function(e){for(var n,t=1,r=arguments.length;t&lt;r;t++)for(var a in n=arguments[t])Object.prototype.hasOwnProperty.call(n,a)&amp;&amp;(e[a]=n[a]);return e},r.apply(this,arguments)};function a(e,n){var t={};for(var r in e)Object.prototype.hasOwnProperty.call(e,r)&amp;&amp;n.indexOf(r)&lt;0&amp;&amp;(t[r]=e[r]);if(null!=e&amp;&amp;"function"==typeof Object.getOwnPropertySymbols){var a=0;for(r=Object.getOwnPropertySymbols(e);a&lt;r.length;a++)n.indexOf(r[a])&lt;0&amp;&amp;Object.prototype.propertyIsEnumerable.call(e,r[a])&amp;&amp;(t[r[a]]=e[r[a]])}return t}function o(e,n,t){if(t||2===arguments.length)for(var r,a=0,o=n.length;a&lt;o;a++)!r&amp;&amp;a in n||(r||(r=Array.prototype.slice.call(n,0,a)),r[a]=n[a]);return e.concat(r||Array.prototype.slice.call(n))}Object.create,Object.create,"function"==typeof SuppressedError&amp;&amp;SuppressedError},1647:(e,n,t)=&gt;{"use strict";t.d(n,{A:()=&gt;r});const r=(0,t(3579).A)((function(e){return null==e}))},1752:(e,n,t)=&gt;{"use strict";t.d(n,{v:()=&gt;a});var r=t(6344);function a(e,n){const t={from:e?.from||n.defaultGradient.from,to:e?.to||n.defaultGradient.to,deg:e?.deg??n.defaultGradient.deg??0},a=(0,r.r)(t.from,n),o=(0,r.r)(t.to,n);return`linear-gradient(${t.deg}deg, ${a} 0%, ${o} 100%)`}},1797:(e,n,t)=&gt;{"use strict";t.d(n,{i:()=&gt;d});var r=t(4848),a=t(295),o=t(2820);function i(e,n,t,r){return"center"===e||"center"===r?{top:n}:"end"===e?{bottom:t}:"start"===e?{top:t}:{}}function s(e,n,t,r,a){return"center"===e||"center"===r?{left:n}:"end"===e?{["ltr"===a?"right":"left"]:t}:"start"===e?{["ltr"===a?"left":"right"]:t}:{}}const l={bottom:"borderTopLeftRadius",left:"borderTopRightRadius",right:"borderBottomLeftRadius",top:"borderBottomRightRadius"};function c({position:e,arrowSize:n,arrowOffset:t,arrowRadius:r,arrowPosition:a,arrowX:o,arrowY:c,dir:d}){const[u,m="center"]=e.split("-"),p={width:n,height:n,transform:"rotate(45deg)",position:"absolute",[l[u]]:r},f=-n/2;return"left"===u?{...p,...i(m,c,t,a),right:f,borderLeftColor:"transparent",borderBottomColor:"transparent",clipPath:"polygon(100% 0, 0 0, 100% 100%)"}:"right"===u?{...p,...i(m,c,t,a),left:f,borderRightColor:"transparent",borderTopColor:"transparent",clipPath:"polygon(0 100%, 0 0, 100% 100%)"}:"top"===u?{...p,...s(m,o,t,a,d),bottom:f,borderTopColor:"transparent",borderLeftColor:"transparent",clipPath:"polygon(0 100%, 100% 100%, 100% 0)"}:"bottom"===u?{...p,...s(m,o,t,a,d),top:f,borderBottomColor:"transparent",borderRightColor:"transparent",clipPath:"polygon(0 100%, 0 0, 100% 0)"}:{}}const d=(0,a.forwardRef)((({position:e,arrowSize:n,arrowOffset:t,arrowRadius:a,arrowPosition:i,visible:s,arrowX:l,arrowY:d,style:u,...m},p)=&gt;{const{dir:f}=(0,o.jH)();return s?(0,r.jsx)("div",{...m,ref:p,style:{...u,...c({position:e,arrowSize:n,arrowOffset:t,arrowRadius:a,arrowPosition:i,dir:f,arrowX:l,arrowY:d})}}):null}));d.displayName="@mantine/core/FloatingArrow"},2254:(e,n,t)=&gt;{"use strict";t.d(n,{A:()=&gt;o});var r=t(3579),a=t(2808);function o(e){return function n(t,o){switch(arguments.length){case 0:return n;case 1:return(0,a.A)(t)?n:(0,r.A)((function(n){return e(t,n)}));default:return(0,a.A)(t)&amp;&amp;(0,a.A)(o)?n:(0,a.A)(t)?(0,r.A)((function(n){return e(n,o)})):(0,a.A)(o)?(0,r.A)((function(n){return e(t,n)})):e(t,o)}}}},2273:(e,n,t)=&gt;{"use strict";t.d(n,{E:()=&gt;o});var r=t(295),a=t(297);function o({opened:e,shouldReturnFocus:n=!0}){const t=(0,r.useRef)(null),o=()=&gt;{t.current&amp;&amp;"focus"in t.current&amp;&amp;"function"==typeof t.current.focus&amp;&amp;t.current?.focus({preventScroll:!0})};return(0,a.C)((()=&gt;{let r=-1;const a=e=&gt;{"Tab"===e.key&amp;&amp;window.clearTimeout(r)};return document.addEventListener("keydown",a),e?t.current=document.activeElement:n&amp;&amp;(r=window.setTimeout(o,10)),()=&gt;{window.clearTimeout(r),document.removeEventListener("keydown",a)}}),[e,n]),o}},2335:(e,n,t)=&gt;{"use strict";t.d(n,{m:()=&gt;B});var r=t(4848),a=t(295),o=t(4164),i=t(7055),s=t(9178),l=t(8690),c=t(6324),d=t(2467),u=t(9396),m=t(6100),p=t(2837),f=t(4791),h=t(2412),v=t(2820),g=t(1797),b=t(9598),y=t(9268),w=t(3087);const _={duration:100,transition:"fade"};var x=t(6344),C=t(1101),k=t(7500),S=t(3505),P=t(4743),N=t(6635),z={tooltip:"m_1b3c8819",arrow:"m_f898399f"};const D={refProp:"ref",withinPortal:!0,offset:10,position:"right",zIndex:(0,l.I)("popover")},E=(0,u.V)(((e,{radius:n,color:t})=&gt;({tooltip:{"--tooltip-radius":void 0===n?void 0:(0,c.nJ)(n),"--tooltip-bg":t?(0,x.r)(t,e):void 0,"--tooltip-color":t?"var(--mantine-color-white)":void 0}}))),j=(0,h.P9)(((e,n)=&gt;{const t=(0,m.Y)("TooltipFloating",D,e),{children:o,refProp:l,withinPortal:c,style:u,className:h,classNames:v,styles:g,unstyled:b,radius:w,color:_,label:x,offset:j,position:A,multiline:I,zIndex:T,disabled:M,defaultOpened:O,variant:R,vars:L,portalProps:Y,...$}=t,F=(0,C.xd)(),B=(0,p.I)({name:"TooltipFloating",props:t,classes:z,className:h,style:u,classNames:v,styles:g,unstyled:b,rootSelector:"tooltip",vars:L,varsResolver:E}),{handleMouseMove:V,x:H,y:W,opened:q,boundaryRef:G,floating:K,setOpened:U}=function({offset:e,position:n,defaultOpened:t}){const[r,o]=(0,a.useState)(t),i=(0,a.useRef)(null),{x:s,y:l,elements:c,refs:d,update:u,placement:m}=(0,S.we)({placement:n,middleware:[(0,P.BN)({crossAxis:!0,padding:5,rootBoundary:"document"})]}),p=m.includes("right")?e:n.includes("left")?-1*e:0,f=m.includes("bottom")?e:n.includes("top")?-1*e:0,h=(0,a.useCallback)((({clientX:e,clientY:n})=&gt;{d.setPositionReference({getBoundingClientRect:()=&gt;({width:0,height:0,x:e,y:n,left:e+p,top:n+f,right:e,bottom:n})})}),[c.reference]);return(0,a.useEffect)((()=&gt;{if(d.floating.current){const e=i.current;e.addEventListener("mousemove",h);const n=(0,N.v9)(d.floating.current);return n.forEach((e=&gt;{e.addEventListener("scroll",u)})),()=&gt;{e.removeEventListener("mousemove",h),n.forEach((e=&gt;{e.removeEventListener("scroll",u)}))}}}),[c.reference,d.floating.current,u,h,r]),{handleMouseMove:h,x:s,y:l,opened:r,setOpened:o,boundaryRef:i,floating:d.setFloating}}({offset:j,position:A,defaultOpened:O});if(!(0,s.v)(o))throw new Error("[@mantine/core] Tooltip.Floating component children should be an element or a component that accepts ref, fragments, strings, numbers and other primitive values are not supported");const Z=(0,i.pc)(G,(0,d.x)(o),n),J=o.props;return(0,r.jsxs)(r.Fragment,{children:[(0,r.jsx)(y.r,{...Y,withinPortal:c,children:(0,r.jsx)(f.a,{...$,...B("tooltip",{style:{...(0,k.X)(u,F),zIndex:T,display:!M&amp;&amp;q?"block":"none",top:(W&amp;&amp;Math.round(W))??"",left:(H&amp;&amp;Math.round(H))??""}}),variant:R,ref:K,mod:{multiline:I},children:x})}),(0,a.cloneElement)(o,{...J,[l]:Z,onMouseEnter:e=&gt;{J.onMouseEnter?.(e),V(e),U(!0)},onMouseLeave:e=&gt;{J.onMouseLeave?.(e),U(!1)}})]})}));j.classes=z,j.displayName="@mantine/core/TooltipFloating";const A=(0,a.createContext)(!1),I=A.Provider,T={openDelay:0,closeDelay:0};function M(e){const{openDelay:n,closeDelay:t,children:a}=(0,m.Y)("TooltipGroup",T,e);return(0,r.jsx)(I,{value:!0,children:(0,r.jsx)(S.T3,{delay:{open:n,close:t},children:a})})}M.displayName="@mantine/core/TooltipGroup",M.extend=e=&gt;e;var O=t(7315),R=t(6284),L=t(297);function Y(e){const n=function(e){if(void 0===e)return{shift:!0,flip:!0};const n={...e};return void 0===e.shift&amp;&amp;(n.shift=!0),void 0===e.flip&amp;&amp;(n.flip=!0),n}(e.middlewares),t=[(0,P.cY)(e.offset)];return n.shift&amp;&amp;t.push((0,P.BN)("boolean"==typeof n.shift?{padding:8}:{padding:8,...n.shift})),n.flip&amp;&amp;t.push("boolean"==typeof n.flip?(0,P.UU)():(0,P.UU)(n.flip)),t.push((0,P.UE)({element:e.arrowRef,padding:e.arrowOffset})),n.inline?t.push("boolean"==typeof n.inline?(0,P.mG)():(0,P.mG)(n.inline)):e.inline&amp;&amp;t.push((0,P.mG)()),t}const $={position:"top",refProp:"ref",withinPortal:!0,arrowSize:4,arrowOffset:5,arrowRadius:0,arrowPosition:"side",offset:5,transitionProps:{duration:100,transition:"fade"},events:{hover:!0,focus:!1,touch:!1},zIndex:(0,l.I)("popover"),positionDependencies:[],middlewares:{flip:!0,shift:!0,inline:!1}},F=(0,u.V)(((e,{radius:n,color:t,variant:r,autoContrast:a})=&gt;{const o=e.variantColorResolver({theme:e,color:t||e.primaryColor,autoContrast:a,variant:r||"filled"});return{tooltip:{"--tooltip-radius":void 0===n?void 0:(0,c.nJ)(n),"--tooltip-bg":t?o.background:void 0,"--tooltip-color":t?o.color:void 0}}})),B=(0,h.P9)(((e,n)=&gt;{const t=(0,m.Y)("Tooltip",$,e),{children:l,position:c,refProp:u,label:h,openDelay:x,closeDelay:C,onPositionChange:k,opened:P,defaultOpened:N,withinPortal:D,radius:E,color:j,classNames:I,styles:T,unstyled:M,style:B,className:V,withArrow:H,arrowSize:W,arrowOffset:q,arrowRadius:G,arrowPosition:K,offset:U,transitionProps:Z,multiline:J,events:X,zIndex:Q,disabled:ee,positionDependencies:ne,onClick:te,onMouseEnter:re,onMouseLeave:ae,inline:oe,variant:ie,keepMounted:se,vars:le,portalProps:ce,mod:de,floatingStrategy:ue,middlewares:me,autoContrast:pe,...fe}=(0,m.Y)("Tooltip",$,t),{dir:he}=(0,v.jH)(),ve=(0,a.useRef)(null),ge=function(e){const[n,t]=(0,a.useState)(e.defaultOpened),r="boolean"==typeof e.opened?e.opened:n,o=(0,a.useContext)(A),i=(0,R.B)(),s=(0,a.useCallback)((e=&gt;{t(e),e&amp;&amp;g(i)}),[i]),{x:l,y:c,context:d,refs:u,placement:m,middlewareData:{arrow:{x:p,y:f}={}}}=(0,S.we)({strategy:e.strategy,placement:e.position,open:r,onOpenChange:s,middleware:Y(e),whileElementsMounted:O.ll}),{delay:h,currentId:v,setCurrentId:g}=(0,S.ck)(d,{id:i}),{getReferenceProps:b,getFloatingProps:y}=(0,S.bv)([(0,S.Mk)(d,{enabled:e.events?.hover,delay:o?h:{open:e.openDelay,close:e.closeDelay},mouseOnly:!e.events?.touch}),(0,S.iQ)(d,{enabled:e.events?.focus,visibleOnly:!0}),(0,S.It)(d,{role:"tooltip"}),(0,S.s9)(d,{enabled:void 0===e.opened})]);(0,L.C)((()=&gt;{e.onPositionChange?.(m)}),[m]);const w=r&amp;&amp;v&amp;&amp;v!==i;return{x:l,y:c,arrowX:p,arrowY:f,reference:u.setReference,floating:u.setFloating,getFloatingProps:y,getReferenceProps:b,isGroupPhase:w,opened:r,placement:m}}({position:(0,b.Q)(he,c),closeDelay:C,openDelay:x,onPositionChange:k,opened:P,defaultOpened:N,events:X,arrowRef:ve,arrowOffset:q,offset:"number"==typeof U?U+(H?W/2:0):U,positionDependencies:[...ne,l],inline:oe,strategy:ue,middlewares:me}),be=(0,p.I)({name:"Tooltip",props:t,classes:z,className:V,style:B,classNames:I,styles:T,unstyled:M,rootSelector:"tooltip",vars:le,varsResolver:F});if(!(0,s.v)(l))throw new Error("[@mantine/core] Tooltip component children should be an element or a component that accepts ref, fragments, strings, numbers and other primitive values are not supported");const ye=(0,i.pc)(ge.reference,(0,d.x)(l),n),we=function(e){return{..._,duration:100,transition:"fade",...e}}(Z),_e=l.props;return(0,r.jsxs)(r.Fragment,{children:[(0,r.jsx)(y.r,{...ce,withinPortal:D,children:(0,r.jsx)(w.e,{...we,keepMounted:se,mounted:!ee&amp;&amp;!!ge.opened,duration:ge.isGroupPhase?10:we.duration,children:e=&gt;(0,r.jsxs)(f.a,{...fe,"data-fixed":"fixed"===ue||void 0,variant:ie,mod:[{multiline:J},de],...ge.getFloatingProps({ref:ge.floating,className:be("tooltip").className,style:{...be("tooltip").style,...e,zIndex:Q,top:ge.y??0,left:ge.x??0}}),children:[h,(0,r.jsx)(g.i,{ref:ve,arrowX:ge.arrowX,arrowY:ge.arrowY,visible:H,position:ge.placement,arrowSize:W,arrowOffset:q,arrowRadius:G,arrowPosition:K,...be("arrow")})]})})}),(0,a.cloneElement)(l,ge.getReferenceProps({onClick:te,onMouseEnter:re,onMouseLeave:ae,onMouseMove:t.onMouseMove,onPointerDown:t.onPointerDown,onPointerEnter:t.onPointerEnter,className:(0,o.A)(V,_e.className),..._e,[u]:ye}))]})}));B.classes=z,B.displayName="@mantine/core/Tooltip",B.Floating=j,B.Group=M},2412:(e,n,t)=&gt;{"use strict";t.d(n,{D_:()=&gt;o,LE:()=&gt;i,P9:()=&gt;s});var r=t(4848),a=t(295);function o(e){return e}function i(e){const n=e;return e=&gt;{const t=(0,a.forwardRef)(((t,a)=&gt;(0,r.jsx)(n,{...e,...t,ref:a})));return t.extend=n.extend,t.displayName=`WithProps(${n.displayName})`,t}}function s(e){const n=(0,a.forwardRef)(e);return n.extend=o,n.withProps=e=&gt;{const t=(0,a.forwardRef)(((t,a)=&gt;(0,r.jsx)(n,{...e,...t,ref:a})));return t.extend=n.extend,t.displayName=`WithProps(${n.displayName})`,t},n}},2467:(e,n,t)=&gt;{"use strict";t.d(n,{x:()=&gt;a});var r=t(295);function a(e){const n=r.version;return"string"!=typeof r.version||n.startsWith("18.")?e?.ref:e?.props?.ref}},2543:function(e,n,t){var r;e=t.nmd(e),function(){var a,o="Expected a function",i="__lodash_hash_undefined__",s="__lodash_placeholder__",l=32,c=128,d=1/0,u=9007199254740991,m=NaN,p=4294967295,f=[["ary",c],["bind",1],["bindKey",2],["curry",8],["curryRight",16],["flip",512],["partial",l],["partialRight",64],["rearg",256]],h="[object Arguments]",v="[object Array]",g="[object Boolean]",b="[object Date]",y="[object Error]",w="[object Function]",_="[object GeneratorFunction]",x="[object Map]",C="[object Number]",k="[object Object]",S="[object Promise]",P="[object RegExp]",N="[object Set]",z="[object String]",D="[object Symbol]",E="[object WeakMap]",j="[object ArrayBuffer]",A="[object DataView]",I="[object Float32Array]",T="[object Float64Array]",M="[object Int8Array]",O="[object Int16Array]",R="[object Int32Array]",L="[object Uint8Array]",Y="[object Uint8ClampedArray]",$="[object Uint16Array]",F="[object Uint32Array]",B=/\b__p \+= '';/g,V=/\b(__p \+=) '' \+/g,H=/(__e\(.*?\)|\b__t\)) \+\n'';/g,W=/&amp;(?:amp|lt|gt|quot|#39);/g,q=/[&amp;&lt;&gt;"']/g,G=RegExp(W.source),K=RegExp(q.source),U=/&lt;%-([\s\S]+?)%&gt;/g,Z=/&lt;%([\s\S]+?)%&gt;/g,J=/&lt;%=([\s\S]+?)%&gt;/g,X=/\.|\[(?:[^[\]]*|(["'])(?:(?!\1)[^\\]|\\.)*?\1)\]/,Q=/^\w*$/,ee=/[^.[\]]+|\[(?:(-?\d+(?:\.\d+)?)|(["'])((?:(?!\2)[^\\]|\\.)*?)\2)\]|(?=(?:\.|\[\])(?:\.|\[\]|$))/g,ne=/[\\^$.*+?()[\]{}|]/g,te=RegExp(ne.source),re=/^\s+/,ae=/\s/,oe=/\{(?:\n\/\* \[wrapped with .+\] \*\/)?\n?/,ie=/\{\n\/\* \[wrapped with (.+)\] \*/,se=/,? &amp; /,le=/[^\x00-\x2f\x3a-\x40\x5b-\x60\x7b-\x7f]+/g,ce=/[()=,{}\[\]\/\s]/,de=/\\(\\)?/g,ue=/\$\{([^\\}]*(?:\\.[^\\}]*)*)\}/g,me=/\w*$/,pe=/^[-+]0x[0-9a-f]+$/i,fe=/^0b[01]+$/i,he=/^\[object .+?Constructor\]$/,ve=/^0o[0-7]+$/i,ge=/^(?:0|[1-9]\d*)$/,be=/[\xc0-\xd6\xd8-\xf6\xf8-\xff\u0100-\u017f]/g,ye=/($^)/,we=/['\n\r\u2028\u2029\\]/g,_e="\\ud800-\\udfff",xe="\\u0300-\\u036f\\ufe20-\\ufe2f\\u20d0-\\u20ff",Ce="\\u2700-\\u27bf",ke="a-z\\xdf-\\xf6\\xf8-\\xff",Se="A-Z\\xc0-\\xd6\\xd8-\\xde",Pe="\\ufe0e\\ufe0f",Ne="\\xac\\xb1\\xd7\\xf7\\x00-\\x2f\\x3a-\\x40\\x5b-\\x60\\x7b-\\xbf\\u2000-\\u206f \\t\\x0b\\f\\xa0\\ufeff\\n\\r\\u2028\\u2029\\u1680\\u180e\\u2000\\u2001\\u2002\\u2003\\u2004\\u2005\\u2006\\u2007\\u2008\\u2009\\u200a\\u202f\\u205f\\u3000",ze="["+_e+"]",De="["+Ne+"]",Ee="["+xe+"]",je="\\d+",Ae="["+Ce+"]",Ie="["+ke+"]",Te="[^"+_e+Ne+je+Ce+ke+Se+"]",Me="\\ud83c[\\udffb-\\udfff]",Oe="[^"+_e+"]",Re="(?:\\ud83c[\\udde6-\\uddff]){2}",Le="[\\ud800-\\udbff][\\udc00-\\udfff]",Ye="["+Se+"]",$e="\\u200d",Fe="(?:"+Ie+"|"+Te+")",Be="(?:"+Ye+"|"+Te+")",Ve="(?:['’](?:d|ll|m|re|s|t|ve))?",He="(?:['’](?:D|LL|M|RE|S|T|VE))?",We="(?:"+Ee+"|"+Me+")?",qe="["+Pe+"]?",Ge=qe+We+"(?:"+$e+"(?:"+[Oe,Re,Le].join("|")+")"+qe+We+")*",Ke="(?:"+[Ae,Re,Le].join("|")+")"+Ge,Ue="(?:"+[Oe+Ee+"?",Ee,Re,Le,ze].join("|")+")",Ze=RegExp("['’]","g"),Je=RegExp(Ee,"g"),Xe=RegExp(Me+"(?="+Me+")|"+Ue+Ge,"g"),Qe=RegExp([Ye+"?"+Ie+"+"+Ve+"(?="+[De,Ye,"$"].join("|")+")",Be+"+"+He+"(?="+[De,Ye+Fe,"$"].join("|")+")",Ye+"?"+Fe+"+"+Ve,Ye+"+"+He,"\\d*(?:1ST|2ND|3RD|(?![123])\\dTH)(?=\\b|[a-z_])","\\d*(?:1st|2nd|3rd|(?![123])\\dth)(?=\\b|[A-Z_])",je,Ke].join("|"),"g"),en=RegExp("["+$e+_e+xe+Pe+"]"),nn=/[a-z][A-Z]|[A-Z]{2}[a-z]|[0-9][a-zA-Z]|[a-zA-Z][0-9]|[^a-zA-Z0-9 ]/,tn=["Array","Buffer","DataView","Date","Error","Float32Array","Float64Array","Function","Int8Array","Int16Array","Int32Array","Map","Math","Object","Promise","RegExp","Set","String","Symbol","TypeError","Uint8Array","Uint8ClampedArray","Uint16Array","Uint32Array","WeakMap","_","clearTimeout","isFinite","parseInt","setTimeout"],rn=-1,an={};an[I]=an[T]=an[M]=an[O]=an[R]=an[L]=an[Y]=an[$]=an[F]=!0,an[h]=an[v]=an[j]=an[g]=an[A]=an[b]=an[y]=an[w]=an[x]=an[C]=an[k]=an[P]=an[N]=an[z]=an[E]=!1;var on={};on[h]=on[v]=on[j]=on[A]=on[g]=on[b]=on[I]=on[T]=on[M]=on[O]=on[R]=on[x]=on[C]=on[k]=on[P]=on[N]=on[z]=on[D]=on[L]=on[Y]=on[$]=on[F]=!0,on[y]=on[w]=on[E]=!1;var sn={"\\":"\\","'":"'","\n":"n","\r":"r","\u2028":"u2028","\u2029":"u2029"},ln=parseFloat,cn=parseInt,dn="object"==typeof t.g&amp;&amp;t.g&amp;&amp;t.g.Object===Object&amp;&amp;t.g,un="object"==typeof self&amp;&amp;self&amp;&amp;self.Object===Object&amp;&amp;self,mn=dn||un||Function("return this")(),pn=n&amp;&amp;!n.nodeType&amp;&amp;n,fn=pn&amp;&amp;e&amp;&amp;!e.nodeType&amp;&amp;e,hn=fn&amp;&amp;fn.exports===pn,vn=hn&amp;&amp;dn.process,gn=function(){try{return fn&amp;&amp;fn.require&amp;&amp;fn.require("util").types||vn&amp;&amp;vn.binding&amp;&amp;vn.binding("util")}catch(e){}}(),bn=gn&amp;&amp;gn.isArrayBuffer,yn=gn&amp;&amp;gn.isDate,wn=gn&amp;&amp;gn.isMap,_n=gn&amp;&amp;gn.isRegExp,xn=gn&amp;&amp;gn.isSet,Cn=gn&amp;&amp;gn.isTypedArray;function kn(e,n,t){switch(t.length){case 0:return e.call(n);case 1:return e.call(n,t[0]);case 2:return e.call(n,t[0],t[1]);case 3:return e.call(n,t[0],t[1],t[2])}return e.apply(n,t)}function Sn(e,n,t,r){for(var a=-1,o=null==e?0:e.length;++a&lt;o;){var i=e[a];n(r,i,t(i),e)}return r}function Pn(e,n){for(var t=-1,r=null==e?0:e.length;++t&lt;r&amp;&amp;!1!==n(e[t],t,e););return e}function Nn(e,n){for(var t=null==e?0:e.length;t--&amp;&amp;!1!==n(e[t],t,e););return e}function zn(e,n){for(var t=-1,r=null==e?0:e.length;++t&lt;r;)if(!n(e[t],t,e))return!1;return!0}function Dn(e,n){for(var t=-1,r=null==e?0:e.length,a=0,o=[];++t&lt;r;){var i=e[t];n(i,t,e)&amp;&amp;(o[a++]=i)}return o}function En(e,n){return!(null==e||!e.length)&amp;&amp;$n(e,n,0)&gt;-1}function jn(e,n,t){for(var r=-1,a=null==e?0:e.length;++r&lt;a;)if(t(n,e[r]))return!0;return!1}function An(e,n){for(var t=-1,r=null==e?0:e.length,a=Array(r);++t&lt;r;)a[t]=n(e[t],t,e);return a}function In(e,n){for(var t=-1,r=n.length,a=e.length;++t&lt;r;)e[a+t]=n[t];return e}function Tn(e,n,t,r){var a=-1,o=null==e?0:e.length;for(r&amp;&amp;o&amp;&amp;(t=e[++a]);++a&lt;o;)t=n(t,e[a],a,e);return t}function Mn(e,n,t,r){var a=null==e?0:e.length;for(r&amp;&amp;a&amp;&amp;(t=e[--a]);a--;)t=n(t,e[a],a,e);return t}function On(e,n){for(var t=-1,r=null==e?0:e.length;++t&lt;r;)if(n(e[t],t,e))return!0;return!1}var Rn=Hn("length");function Ln(e,n,t){var r;return t(e,(function(e,t,a){if(n(e,t,a))return r=t,!1})),r}function Yn(e,n,t,r){for(var a=e.length,o=t+(r?1:-1);r?o--:++o&lt;a;)if(n(e[o],o,e)</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/svg</t>
+  </si>
+  <si>
+    <t>u20ff</t>
+  </si>
+  <si>
+    <t>C:\AAYS_GITHUB_BRIDGE_CLEAN2\ai-data\ty150-nista-pipeline-deep-discovery\raw\https___unpkg.com_dash_mantine_components_2.1.0_dash_mantine_components_dash_mantine_components.js.txt</t>
+  </si>
+  <si>
+    <t>EA-REVIEW-EA-CAND-000072</t>
+  </si>
+  <si>
+    <t>EA-CAND-000072</t>
+  </si>
+  <si>
+    <t>381988,53.445665997]},"properties":{"listing_id":"OTM-16266373","source_name":"market_listing_adapter","pr</t>
+  </si>
+  <si>
+    <t>Dagenham, Essex, RM8 3PA","local_authority":"Barking and Dagenham","postcode":"RM8 3PA","listing_status":</t>
+  </si>
+  <si>
+    <t>http://localhost:8010/health</t>
+  </si>
+  <si>
+    <t>RM8 3PA</t>
+  </si>
+  <si>
+    <t>C:\AAYS_GITHUB_BRIDGE_CLEAN2\ai-results\2026-05-02_22-46-55-terrayield-long-diagnostic-001.md</t>
+  </si>
+  <si>
+    <t>evidence_id</t>
+  </si>
+  <si>
+    <t>evidence_type</t>
+  </si>
+  <si>
+    <t>field_supported</t>
+  </si>
+  <si>
+    <t>truth_score_4</t>
+  </si>
+  <si>
+    <t>evidence_summary</t>
+  </si>
+  <si>
+    <t>verified_at</t>
+  </si>
+  <si>
+    <t>EVID-FINAL-EA-CAND-000020</t>
+  </si>
+  <si>
+    <t>local_source_text</t>
+  </si>
+  <si>
+    <t>company;phone;url;postcode</t>
+  </si>
+  <si>
+    <t>Source file contained company-like line plus extracted phone/url/postcode.</t>
+  </si>
+  <si>
+    <t>2026-05-24T02:18:18</t>
+  </si>
+  <si>
+    <t>No DB write. No production import.</t>
+  </si>
+  <si>
+    <t>EVID-FINAL-EA-CAND-000023</t>
+  </si>
+  <si>
+    <t>EVID-FINAL-EA-CAND-000028</t>
+  </si>
+  <si>
+    <t>EVID-FINAL-EA-CAND-000072</t>
+  </si>
+  <si>
+    <t>parcel_group_id</t>
+  </si>
+  <si>
+    <t>coverage_method</t>
+  </si>
+  <si>
+    <t>coverage_truth_score_4</t>
+  </si>
+  <si>
+    <t>ENG-PG-102</t>
+  </si>
+  <si>
+    <t>derived_from_geometry_centroid_join</t>
+  </si>
+  <si>
+    <t>Coverage from geometry centroid join. Review before DB import.</t>
+  </si>
+  <si>
+    <t>ENG-PG-016</t>
+  </si>
+  <si>
+    <t>ENG-PG-096</t>
+  </si>
+  <si>
+    <t>program_parcel_id</t>
+  </si>
+  <si>
+    <t>match_method</t>
+  </si>
+  <si>
+    <t>match_confidence</t>
+  </si>
+  <si>
+    <t>geometry_field</t>
+  </si>
+  <si>
+    <t>midlands</t>
+  </si>
+  <si>
+    <t>geometry_centroid_inside_200_group_bbox</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\AAYS_MVP_Streamlit_Studio_v3_ScenarioEngine_ConfigWizard\pipeline\reports\region_geometry_v2\midlands.json</t>
+  </si>
+  <si>
+    <t>json_or_geojson</t>
+  </si>
+  <si>
+    <t>Centroid extracted from geometry/WKT/GeoJSON and matched to 200 group bbox. Review before DB import.</t>
+  </si>
+  <si>
+    <t>FINAL_3110_CURRENT_CONFIDENCE.points</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\data\FINAL_3110_CURRENT_CONFIDENCE.points.geojson</t>
+  </si>
+  <si>
+    <t>FINAL_3110_CURRENT_CONFIDENCE.polygons</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\data\FINAL_3110_CURRENT_CONFIDENCE.polygons.geojson</t>
+  </si>
+  <si>
+    <t>pmtiles_regions_full_england</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\pmtiles_regions_full_england.json</t>
+  </si>
+  <si>
+    <t>lon</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>point_count</t>
+  </si>
+  <si>
+    <t>parse_method</t>
+  </si>
+  <si>
+    <t>53,02</t>
+  </si>
+  <si>
+    <t>json_geojson_numeric_centroid</t>
+  </si>
+  <si>
+    <t>-0,120289498355555</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\aays\london_parcel_topography_confidence\parcel_topography_L4_HIGH_sample.geojson</t>
+  </si>
+  <si>
+    <t>0,166417325866668</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\aays\london_parcel_topography_confidence\parcel_topography_L2_MEDIUM_sample.geojson</t>
+  </si>
+  <si>
+    <t>56,4</t>
+  </si>
+  <si>
+    <t>-0,0486127923000001</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\aays\london_parcel_topography_confidence\parcel_topography_sample_points.geojson</t>
+  </si>
+  <si>
+    <t>pmtiles_regions_full_scotland</t>
+  </si>
+  <si>
+    <t>-4,1</t>
+  </si>
+  <si>
+    <t>56,75</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\pmtiles_regions_full_scotland.json</t>
+  </si>
+  <si>
+    <t>pmtiles_regions_scotland_generated_v1</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\pmtiles_regions_scotland_generated_v1.json</t>
+  </si>
+  <si>
+    <t>pmtiles_regions_england_generated_v2</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\pmtiles_regions_england_generated_v2.json</t>
+  </si>
+  <si>
+    <t>-1,4</t>
+  </si>
+  <si>
+    <t>52,27</t>
+  </si>
+  <si>
+    <t>pmtiles_regions_england_generated</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\pmtiles_regions_england_generated.json</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\public\aays\london_parcel_topography_confidence\parcel_topography_L4_HIGH_sample.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\public\aays\london_parcel_topography_confidence\parcel_topography_sample_points.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\public\aays\london_parcel_topography_confidence\parcel_topography_L2_MEDIUM_sample.geojson</t>
+  </si>
+  <si>
+    <t>market_listing_parcel_edges_20260423</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\exports\market_listing_parcel_package\market_listing_parcel_edges_20260423.geojson</t>
+  </si>
+  <si>
+    <t>market_listing_parcel_edges_20260422</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\exports\market_listing_parcel_package\market_listing_parcel_edges_20260422.geojson</t>
+  </si>
+  <si>
+    <t>endpoint__map_sales-history_parcels</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\.aays_next_fix\run_20260502_191619\endpoint__map_sales-history_parcels.json</t>
+  </si>
+  <si>
+    <t>air_quality_laqn_latest</t>
+  </si>
+  <si>
+    <t>-0,113362508423829</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step16_preleaflet_hook_working_panel_20260430_214948\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step15_real_map_capture_working_buttons_20260430_214334\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>air_quality_england_unified</t>
+  </si>
+  <si>
+    <t>-0,939241025652445</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\data\air_quality_england_unified.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step18_visual_aq_overlay_and_working_buttons_20260430_220505\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step17_dom_panel_no_map_capture_dependency_20260430_215556\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step14_hard_fix_nonoverlap_clickable_panel_20260430_213327\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step18_visual_aq_overlay_and_working_buttons_20260430_221328\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>north-points</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\data\poi\north-points.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step29_deferred_gl_terrain_real_fix_20260501_001006\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step28_engine_agnostic_layers_retry_selftest_20260501_000330\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step25_safe_leaflet_capture_no_appjs_break_20260430_233935\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step19_toolbar_integrated_tile_based_aq_terrain_20260430_223554\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step24_real_leaflet_layers_selftested_20260430_233200\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step21_real_tile_overlay_terrain_aq_streetview_20260430_230247\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step20_google_like_terrain_aq_toolbar_integration_20260430_224844\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step13_final_nonoverlap_working_buttons_airdata_20260430_212830\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step27_leaflet_runtime_python_cdp_selftest_20260430_235608\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step26_early_leaflet_capture_cdp_selftest_20260430_234518\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\england_map_web\.aays_backups\step11_working_panel_direct_events_data_collect_20260430_211514\data\air_quality_laqn_latest.geojson</t>
+  </si>
+  <si>
+    <t>historic_england_facilities</t>
+  </si>
+  <si>
+    <t>-0,11091</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\live_feeds\facilities\drops\historic_england_facilities.geojson</t>
+  </si>
+  <si>
+    <t>os_ngd_facilities</t>
+  </si>
+  <si>
+    <t>-0,10424</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\live_feeds\facilities\drops\os_ngd_facilities.geojson</t>
+  </si>
+  <si>
+    <t>osm-demo-school-1</t>
+  </si>
+  <si>
+    <t>-0,489666666666667</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\live_feeds\facilities\drops\osm_facilities.geojson</t>
+  </si>
+  <si>
+    <t>os_land_use_features</t>
+  </si>
+  <si>
+    <t>-0,105892</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\live_feeds\facilities\drops\os_land_use_features.geojson</t>
+  </si>
+  <si>
+    <t>naptan_facilities</t>
+  </si>
+  <si>
+    <t>-0,101026666666667</t>
+  </si>
+  <si>
+    <t>C:\Users\cagda\Documents\GitHub\AAYS\terrayield_land_intelligence\data\live_feeds\facilities\drops\naptan_facilities.geojson</t>
   </si>
 </sst>
 </file>
@@ -99,8 +556,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,56 +892,1877 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF47F19-893E-4654-93AF-50950DC34430}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67149764-4C91-41C6-A2E7-D103F1C7A3B3}">
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1">
+        <v>-1425</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>29507001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="1">
+        <v>515003354875774</v>
+      </c>
+      <c r="D3">
+        <v>45000</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>29759443</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="1">
+        <v>516294783376667</v>
+      </c>
+      <c r="D4">
+        <v>15000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>29759443</v>
+      </c>
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="1">
+        <v>515326212000999</v>
+      </c>
+      <c r="D7">
+        <v>60000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-114902222222222</v>
+      </c>
+      <c r="C10" s="1">
+        <v>521690666666667</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-114902222222222</v>
+      </c>
+      <c r="C12" s="1">
+        <v>521690666666667</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>29507001</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="1">
+        <v>515003354875774</v>
+      </c>
+      <c r="D13">
+        <v>45000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>29759443</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="1">
+        <v>515326212000999</v>
+      </c>
+      <c r="D14">
+        <v>60000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>29759443</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="1">
+        <v>516294783376667</v>
+      </c>
+      <c r="D15">
+        <v>15000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-12115691165603</v>
+      </c>
+      <c r="C16" s="1">
+        <v>524859565703005</v>
+      </c>
+      <c r="D16">
+        <v>20432</v>
+      </c>
+      <c r="E16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-12115691165603</v>
+      </c>
+      <c r="C17" s="1">
+        <v>524859565703005</v>
+      </c>
+      <c r="D17">
+        <v>20432</v>
+      </c>
+      <c r="E17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>54</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D19">
+        <v>256</v>
+      </c>
+      <c r="E19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D20">
+        <v>256</v>
+      </c>
+      <c r="E20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="1">
+        <v>519421800310145</v>
+      </c>
+      <c r="D21">
+        <v>794</v>
+      </c>
+      <c r="E21" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D22">
+        <v>256</v>
+      </c>
+      <c r="E22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D23">
+        <v>256</v>
+      </c>
+      <c r="E23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D24">
+        <v>256</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D25">
+        <v>256</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26">
+        <v>53</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D27">
+        <v>256</v>
+      </c>
+      <c r="E27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D28">
+        <v>256</v>
+      </c>
+      <c r="E28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D29">
+        <v>256</v>
+      </c>
+      <c r="E29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D30">
+        <v>256</v>
+      </c>
+      <c r="E30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D31">
+        <v>256</v>
+      </c>
+      <c r="E31" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D32">
+        <v>256</v>
+      </c>
+      <c r="E32" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D33">
+        <v>256</v>
+      </c>
+      <c r="E33" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D34">
+        <v>256</v>
+      </c>
+      <c r="E34" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D35">
+        <v>256</v>
+      </c>
+      <c r="E35" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D36">
+        <v>256</v>
+      </c>
+      <c r="E36" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="1">
+        <v>514918591344741</v>
+      </c>
+      <c r="D37">
+        <v>256</v>
+      </c>
+      <c r="E37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="1">
+        <v>5151686</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="1">
+        <v>515435333333333</v>
+      </c>
+      <c r="D39">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="1">
+        <v>517068</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="1">
+        <v>51548816</v>
+      </c>
+      <c r="D41">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="1">
+        <v>515484333333333</v>
+      </c>
+      <c r="D42">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF10E7C3-C54E-40B3-AF2A-0402233B7AF5}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44690D46-E6C7-460E-B270-963BF9FB3017}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA3E7C3-85AC-4AC6-9C6F-112493F88CF9}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0344BF63-E7D9-47D4-B968-C5325AC043BB}">
+  <dimension ref="A1:R5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>8</v>
+      </c>
+      <c r="O2">
+        <v>4</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3">
+        <v>8</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>719925474</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4">
+        <v>8</v>
+      </c>
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5">
+        <v>113995205</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
